--- a/Odds-Data-Clean/2016-17.xlsx
+++ b/Odds-Data-Clean/2016-17.xlsx
@@ -21666,7 +21666,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2016-17-101</t>
+          <t>2016-17-0101</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -21708,7 +21708,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2016-17-101</t>
+          <t>2016-17-0101</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -21750,7 +21750,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2016-17-101</t>
+          <t>2016-17-0101</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -21792,7 +21792,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2016-17-101</t>
+          <t>2016-17-0101</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2016-17-101</t>
+          <t>2016-17-0101</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2016-17-102</t>
+          <t>2016-17-0102</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2016-17-102</t>
+          <t>2016-17-0102</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2016-17-102</t>
+          <t>2016-17-0102</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -22002,7 +22002,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2016-17-102</t>
+          <t>2016-17-0102</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -22044,7 +22044,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2016-17-102</t>
+          <t>2016-17-0102</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2016-17-102</t>
+          <t>2016-17-0102</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2016-17-102</t>
+          <t>2016-17-0102</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -22170,7 +22170,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2016-17-102</t>
+          <t>2016-17-0102</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2016-17-103</t>
+          <t>2016-17-0103</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -22254,7 +22254,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2016-17-103</t>
+          <t>2016-17-0103</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -22296,7 +22296,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2016-17-103</t>
+          <t>2016-17-0103</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -22338,7 +22338,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2016-17-103</t>
+          <t>2016-17-0103</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -22380,7 +22380,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2016-17-103</t>
+          <t>2016-17-0103</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2016-17-103</t>
+          <t>2016-17-0103</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2016-17-103</t>
+          <t>2016-17-0103</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -22506,7 +22506,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2016-17-103</t>
+          <t>2016-17-0103</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -22548,7 +22548,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2016-17-104</t>
+          <t>2016-17-0104</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -22590,7 +22590,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2016-17-104</t>
+          <t>2016-17-0104</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2016-17-104</t>
+          <t>2016-17-0104</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2016-17-104</t>
+          <t>2016-17-0104</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -22716,7 +22716,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2016-17-104</t>
+          <t>2016-17-0104</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2016-17-104</t>
+          <t>2016-17-0104</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -22800,7 +22800,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2016-17-104</t>
+          <t>2016-17-0104</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -22842,7 +22842,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2016-17-105</t>
+          <t>2016-17-0105</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2016-17-105</t>
+          <t>2016-17-0105</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -22926,7 +22926,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2016-17-105</t>
+          <t>2016-17-0105</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -22968,7 +22968,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2016-17-105</t>
+          <t>2016-17-0105</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -23010,7 +23010,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2016-17-105</t>
+          <t>2016-17-0105</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2016-17-105</t>
+          <t>2016-17-0105</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -23094,7 +23094,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2016-17-105</t>
+          <t>2016-17-0105</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -23136,7 +23136,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2016-17-105</t>
+          <t>2016-17-0105</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -23178,7 +23178,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2016-17-106</t>
+          <t>2016-17-0106</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -23220,7 +23220,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2016-17-106</t>
+          <t>2016-17-0106</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -23262,7 +23262,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2016-17-106</t>
+          <t>2016-17-0106</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -23304,7 +23304,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2016-17-106</t>
+          <t>2016-17-0106</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -23346,7 +23346,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2016-17-106</t>
+          <t>2016-17-0106</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2016-17-106</t>
+          <t>2016-17-0106</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -23430,7 +23430,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2016-17-106</t>
+          <t>2016-17-0106</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -23472,7 +23472,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2016-17-106</t>
+          <t>2016-17-0106</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -23514,7 +23514,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2016-17-107</t>
+          <t>2016-17-0107</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -23556,7 +23556,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2016-17-107</t>
+          <t>2016-17-0107</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -23598,7 +23598,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2016-17-107</t>
+          <t>2016-17-0107</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2016-17-107</t>
+          <t>2016-17-0107</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -23682,7 +23682,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2016-17-107</t>
+          <t>2016-17-0107</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2016-17-107</t>
+          <t>2016-17-0107</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2016-17-107</t>
+          <t>2016-17-0107</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2016-17-108</t>
+          <t>2016-17-0108</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2016-17-108</t>
+          <t>2016-17-0108</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -23892,7 +23892,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>2016-17-108</t>
+          <t>2016-17-0108</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>2016-17-108</t>
+          <t>2016-17-0108</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -23976,7 +23976,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>2016-17-108</t>
+          <t>2016-17-0108</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -24018,7 +24018,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>2016-17-108</t>
+          <t>2016-17-0108</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -24060,7 +24060,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>2016-17-108</t>
+          <t>2016-17-0108</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -24102,7 +24102,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>2016-17-108</t>
+          <t>2016-17-0108</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -24144,7 +24144,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>2016-17-108</t>
+          <t>2016-17-0108</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>2016-17-109</t>
+          <t>2016-17-0109</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>2016-17-109</t>
+          <t>2016-17-0109</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -24270,7 +24270,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>2016-17-109</t>
+          <t>2016-17-0109</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -24312,7 +24312,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>2016-17-110</t>
+          <t>2016-17-0110</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -24354,7 +24354,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>2016-17-110</t>
+          <t>2016-17-0110</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -24396,7 +24396,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>2016-17-110</t>
+          <t>2016-17-0110</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>2016-17-110</t>
+          <t>2016-17-0110</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -24480,7 +24480,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>2016-17-110</t>
+          <t>2016-17-0110</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>2016-17-110</t>
+          <t>2016-17-0110</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -24564,7 +24564,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>2016-17-110</t>
+          <t>2016-17-0110</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -24606,7 +24606,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>2016-17-110</t>
+          <t>2016-17-0110</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>2016-17-110</t>
+          <t>2016-17-0110</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>2016-17-111</t>
+          <t>2016-17-0111</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -24732,7 +24732,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>2016-17-111</t>
+          <t>2016-17-0111</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>2016-17-111</t>
+          <t>2016-17-0111</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -24816,7 +24816,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>2016-17-111</t>
+          <t>2016-17-0111</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -24858,7 +24858,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>2016-17-111</t>
+          <t>2016-17-0111</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -24900,7 +24900,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>2016-17-111</t>
+          <t>2016-17-0111</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -24942,7 +24942,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>2016-17-112</t>
+          <t>2016-17-0112</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>2016-17-112</t>
+          <t>2016-17-0112</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -25026,7 +25026,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>2016-17-112</t>
+          <t>2016-17-0112</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -25068,7 +25068,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>2016-17-112</t>
+          <t>2016-17-0112</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -25110,7 +25110,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>2016-17-112</t>
+          <t>2016-17-0112</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -25152,7 +25152,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>2016-17-112</t>
+          <t>2016-17-0112</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -25194,7 +25194,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>2016-17-113</t>
+          <t>2016-17-0113</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>2016-17-113</t>
+          <t>2016-17-0113</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -25278,7 +25278,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>2016-17-113</t>
+          <t>2016-17-0113</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -25320,7 +25320,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>2016-17-113</t>
+          <t>2016-17-0113</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -25362,7 +25362,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>2016-17-113</t>
+          <t>2016-17-0113</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -25404,7 +25404,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>2016-17-113</t>
+          <t>2016-17-0113</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -25446,7 +25446,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>2016-17-113</t>
+          <t>2016-17-0113</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -25488,7 +25488,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>2016-17-113</t>
+          <t>2016-17-0113</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>2016-17-113</t>
+          <t>2016-17-0113</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -25572,7 +25572,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>2016-17-114</t>
+          <t>2016-17-0114</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -25614,7 +25614,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>2016-17-114</t>
+          <t>2016-17-0114</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -25656,7 +25656,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>2016-17-114</t>
+          <t>2016-17-0114</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -25698,7 +25698,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>2016-17-114</t>
+          <t>2016-17-0114</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -25740,7 +25740,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>2016-17-114</t>
+          <t>2016-17-0114</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -25782,7 +25782,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>2016-17-115</t>
+          <t>2016-17-0115</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -25824,7 +25824,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>2016-17-115</t>
+          <t>2016-17-0115</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -25866,7 +25866,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>2016-17-115</t>
+          <t>2016-17-0115</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -25908,7 +25908,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>2016-17-115</t>
+          <t>2016-17-0115</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -25950,7 +25950,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>2016-17-115</t>
+          <t>2016-17-0115</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>2016-17-115</t>
+          <t>2016-17-0115</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>2016-17-115</t>
+          <t>2016-17-0115</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -26076,7 +26076,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>2016-17-116</t>
+          <t>2016-17-0116</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -26118,7 +26118,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>2016-17-116</t>
+          <t>2016-17-0116</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -26160,7 +26160,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>2016-17-116</t>
+          <t>2016-17-0116</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -26202,7 +26202,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>2016-17-116</t>
+          <t>2016-17-0116</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -26244,7 +26244,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>2016-17-116</t>
+          <t>2016-17-0116</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -26286,7 +26286,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>2016-17-116</t>
+          <t>2016-17-0116</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -26328,7 +26328,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>2016-17-116</t>
+          <t>2016-17-0116</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -26370,7 +26370,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>2016-17-116</t>
+          <t>2016-17-0116</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>2016-17-116</t>
+          <t>2016-17-0116</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -26454,7 +26454,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>2016-17-117</t>
+          <t>2016-17-0117</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -26496,7 +26496,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>2016-17-117</t>
+          <t>2016-17-0117</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -26538,7 +26538,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>2016-17-117</t>
+          <t>2016-17-0117</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -26580,7 +26580,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>2016-17-117</t>
+          <t>2016-17-0117</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -26622,7 +26622,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>2016-17-117</t>
+          <t>2016-17-0117</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -26664,7 +26664,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>2016-17-118</t>
+          <t>2016-17-0118</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -26706,7 +26706,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>2016-17-118</t>
+          <t>2016-17-0118</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -26748,7 +26748,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>2016-17-118</t>
+          <t>2016-17-0118</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -26790,7 +26790,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>2016-17-118</t>
+          <t>2016-17-0118</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>2016-17-118</t>
+          <t>2016-17-0118</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -26874,7 +26874,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>2016-17-118</t>
+          <t>2016-17-0118</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -26916,7 +26916,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>2016-17-118</t>
+          <t>2016-17-0118</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -26958,7 +26958,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>2016-17-118</t>
+          <t>2016-17-0118</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -27000,7 +27000,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>2016-17-118</t>
+          <t>2016-17-0118</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -27042,7 +27042,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>2016-17-119</t>
+          <t>2016-17-0119</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>2016-17-119</t>
+          <t>2016-17-0119</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -27126,7 +27126,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>2016-17-119</t>
+          <t>2016-17-0119</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -27168,7 +27168,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>2016-17-119</t>
+          <t>2016-17-0119</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -27210,7 +27210,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>2016-17-119</t>
+          <t>2016-17-0119</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -27252,7 +27252,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>2016-17-120</t>
+          <t>2016-17-0120</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -27294,7 +27294,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>2016-17-120</t>
+          <t>2016-17-0120</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>2016-17-120</t>
+          <t>2016-17-0120</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -27378,7 +27378,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>2016-17-120</t>
+          <t>2016-17-0120</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -27420,7 +27420,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>2016-17-120</t>
+          <t>2016-17-0120</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -27462,7 +27462,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>2016-17-120</t>
+          <t>2016-17-0120</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -27504,7 +27504,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>2016-17-120</t>
+          <t>2016-17-0120</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -27546,7 +27546,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>2016-17-120</t>
+          <t>2016-17-0120</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -27588,7 +27588,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>2016-17-120</t>
+          <t>2016-17-0120</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -27630,7 +27630,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>2016-17-121</t>
+          <t>2016-17-0121</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>2016-17-121</t>
+          <t>2016-17-0121</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -27714,7 +27714,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>2016-17-121</t>
+          <t>2016-17-0121</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -27756,7 +27756,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>2016-17-121</t>
+          <t>2016-17-0121</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>2016-17-121</t>
+          <t>2016-17-0121</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -27840,7 +27840,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>2016-17-121</t>
+          <t>2016-17-0121</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -27882,7 +27882,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>2016-17-121</t>
+          <t>2016-17-0121</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -27924,7 +27924,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>2016-17-121</t>
+          <t>2016-17-0121</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -27966,7 +27966,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>2016-17-121</t>
+          <t>2016-17-0121</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -28008,7 +28008,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>2016-17-121</t>
+          <t>2016-17-0121</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>2016-17-121</t>
+          <t>2016-17-0121</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -28092,7 +28092,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>2016-17-122</t>
+          <t>2016-17-0122</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -28134,7 +28134,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>2016-17-122</t>
+          <t>2016-17-0122</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -28176,7 +28176,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>2016-17-122</t>
+          <t>2016-17-0122</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -28218,7 +28218,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>2016-17-122</t>
+          <t>2016-17-0122</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -28260,7 +28260,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>2016-17-123</t>
+          <t>2016-17-0123</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -28302,7 +28302,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>2016-17-123</t>
+          <t>2016-17-0123</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -28344,7 +28344,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>2016-17-123</t>
+          <t>2016-17-0123</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -28386,7 +28386,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>2016-17-123</t>
+          <t>2016-17-0123</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -28428,7 +28428,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>2016-17-123</t>
+          <t>2016-17-0123</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -28470,7 +28470,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>2016-17-123</t>
+          <t>2016-17-0123</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -28512,7 +28512,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>2016-17-123</t>
+          <t>2016-17-0123</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -28554,7 +28554,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>2016-17-123</t>
+          <t>2016-17-0123</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>2016-17-123</t>
+          <t>2016-17-0123</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -28638,7 +28638,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>2016-17-124</t>
+          <t>2016-17-0124</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -28680,7 +28680,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>2016-17-124</t>
+          <t>2016-17-0124</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -28722,7 +28722,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>2016-17-124</t>
+          <t>2016-17-0124</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -28764,7 +28764,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>2016-17-124</t>
+          <t>2016-17-0124</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -28806,7 +28806,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>2016-17-124</t>
+          <t>2016-17-0124</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -28848,7 +28848,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>2016-17-124</t>
+          <t>2016-17-0124</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -28890,7 +28890,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>2016-17-125</t>
+          <t>2016-17-0125</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -28932,7 +28932,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>2016-17-125</t>
+          <t>2016-17-0125</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -28974,7 +28974,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>2016-17-125</t>
+          <t>2016-17-0125</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>2016-17-125</t>
+          <t>2016-17-0125</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -29058,7 +29058,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>2016-17-125</t>
+          <t>2016-17-0125</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -29100,7 +29100,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>2016-17-125</t>
+          <t>2016-17-0125</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -29142,7 +29142,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>2016-17-125</t>
+          <t>2016-17-0125</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -29184,7 +29184,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>2016-17-125</t>
+          <t>2016-17-0125</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -29226,7 +29226,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>2016-17-125</t>
+          <t>2016-17-0125</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -29268,7 +29268,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>2016-17-125</t>
+          <t>2016-17-0125</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -29310,7 +29310,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>2016-17-126</t>
+          <t>2016-17-0126</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -29352,7 +29352,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>2016-17-126</t>
+          <t>2016-17-0126</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -29394,7 +29394,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>2016-17-126</t>
+          <t>2016-17-0126</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -29436,7 +29436,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>2016-17-126</t>
+          <t>2016-17-0126</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -29478,7 +29478,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>2016-17-127</t>
+          <t>2016-17-0127</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -29520,7 +29520,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>2016-17-127</t>
+          <t>2016-17-0127</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -29562,7 +29562,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>2016-17-127</t>
+          <t>2016-17-0127</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -29604,7 +29604,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>2016-17-127</t>
+          <t>2016-17-0127</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>2016-17-127</t>
+          <t>2016-17-0127</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -29688,7 +29688,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>2016-17-127</t>
+          <t>2016-17-0127</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -29730,7 +29730,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>2016-17-127</t>
+          <t>2016-17-0127</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>2016-17-127</t>
+          <t>2016-17-0127</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -29814,7 +29814,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>2016-17-127</t>
+          <t>2016-17-0127</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -29856,7 +29856,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>2016-17-127</t>
+          <t>2016-17-0127</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>2016-17-128</t>
+          <t>2016-17-0128</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -29940,7 +29940,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>2016-17-128</t>
+          <t>2016-17-0128</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -29982,7 +29982,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>2016-17-128</t>
+          <t>2016-17-0128</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -30024,7 +30024,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>2016-17-128</t>
+          <t>2016-17-0128</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -30066,7 +30066,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>2016-17-128</t>
+          <t>2016-17-0128</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -30108,7 +30108,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>2016-17-128</t>
+          <t>2016-17-0128</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -30150,7 +30150,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>2016-17-128</t>
+          <t>2016-17-0128</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -30192,7 +30192,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>2016-17-129</t>
+          <t>2016-17-0129</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -30234,7 +30234,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>2016-17-129</t>
+          <t>2016-17-0129</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -30276,7 +30276,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>2016-17-129</t>
+          <t>2016-17-0129</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -30318,7 +30318,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>2016-17-129</t>
+          <t>2016-17-0129</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -30360,7 +30360,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>2016-17-129</t>
+          <t>2016-17-0129</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -30402,7 +30402,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>2016-17-129</t>
+          <t>2016-17-0129</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -30444,7 +30444,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>2016-17-129</t>
+          <t>2016-17-0129</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -30486,7 +30486,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>2016-17-129</t>
+          <t>2016-17-0129</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -30528,7 +30528,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>2016-17-130</t>
+          <t>2016-17-0130</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -30570,7 +30570,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>2016-17-130</t>
+          <t>2016-17-0130</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -30612,7 +30612,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>2016-17-130</t>
+          <t>2016-17-0130</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -30654,7 +30654,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>2016-17-130</t>
+          <t>2016-17-0130</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -30696,7 +30696,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>2016-17-130</t>
+          <t>2016-17-0130</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -30738,7 +30738,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>2016-17-130</t>
+          <t>2016-17-0130</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -30780,7 +30780,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>2016-17-131</t>
+          <t>2016-17-0131</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -30822,7 +30822,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>2016-17-131</t>
+          <t>2016-17-0131</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -30864,7 +30864,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>2016-17-131</t>
+          <t>2016-17-0131</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -30906,7 +30906,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>2016-17-131</t>
+          <t>2016-17-0131</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>2016-17-131</t>
+          <t>2016-17-0131</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -30990,7 +30990,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>2016-17-131</t>
+          <t>2016-17-0131</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -31032,7 +31032,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>2016-17-201</t>
+          <t>2016-17-0201</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>2016-17-201</t>
+          <t>2016-17-0201</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -31116,7 +31116,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>2016-17-201</t>
+          <t>2016-17-0201</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -31158,7 +31158,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>2016-17-201</t>
+          <t>2016-17-0201</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>2016-17-201</t>
+          <t>2016-17-0201</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -31242,7 +31242,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>2016-17-201</t>
+          <t>2016-17-0201</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -31284,7 +31284,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>2016-17-201</t>
+          <t>2016-17-0201</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -31326,7 +31326,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>2016-17-201</t>
+          <t>2016-17-0201</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -31368,7 +31368,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>2016-17-201</t>
+          <t>2016-17-0201</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -31410,7 +31410,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>2016-17-201</t>
+          <t>2016-17-0201</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -31452,7 +31452,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>2016-17-201</t>
+          <t>2016-17-0201</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -31494,7 +31494,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>2016-17-201</t>
+          <t>2016-17-0201</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -31536,7 +31536,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>2016-17-202</t>
+          <t>2016-17-0202</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -31578,7 +31578,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>2016-17-202</t>
+          <t>2016-17-0202</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -31620,7 +31620,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>2016-17-202</t>
+          <t>2016-17-0202</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -31662,7 +31662,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>2016-17-202</t>
+          <t>2016-17-0202</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -31704,7 +31704,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>2016-17-203</t>
+          <t>2016-17-0203</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -31746,7 +31746,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>2016-17-203</t>
+          <t>2016-17-0203</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -31788,7 +31788,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>2016-17-203</t>
+          <t>2016-17-0203</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -31830,7 +31830,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>2016-17-203</t>
+          <t>2016-17-0203</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -31872,7 +31872,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>2016-17-203</t>
+          <t>2016-17-0203</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -31914,7 +31914,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>2016-17-203</t>
+          <t>2016-17-0203</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -31956,7 +31956,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>2016-17-203</t>
+          <t>2016-17-0203</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -31998,7 +31998,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>2016-17-203</t>
+          <t>2016-17-0203</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -32040,7 +32040,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>2016-17-203</t>
+          <t>2016-17-0203</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -32082,7 +32082,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>2016-17-204</t>
+          <t>2016-17-0204</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -32124,7 +32124,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>2016-17-204</t>
+          <t>2016-17-0204</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -32166,7 +32166,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>2016-17-204</t>
+          <t>2016-17-0204</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>2016-17-204</t>
+          <t>2016-17-0204</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -32250,7 +32250,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>2016-17-204</t>
+          <t>2016-17-0204</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -32292,7 +32292,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>2016-17-204</t>
+          <t>2016-17-0204</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -32334,7 +32334,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>2016-17-204</t>
+          <t>2016-17-0204</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -32376,7 +32376,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>2016-17-204</t>
+          <t>2016-17-0204</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -32418,7 +32418,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>2016-17-204</t>
+          <t>2016-17-0204</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -32460,7 +32460,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>2016-17-204</t>
+          <t>2016-17-0204</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -32502,7 +32502,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>2016-17-205</t>
+          <t>2016-17-0205</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -32544,7 +32544,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>2016-17-205</t>
+          <t>2016-17-0205</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -32586,7 +32586,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>2016-17-205</t>
+          <t>2016-17-0205</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -32628,7 +32628,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>2016-17-206</t>
+          <t>2016-17-0206</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -32670,7 +32670,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>2016-17-206</t>
+          <t>2016-17-0206</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -32712,7 +32712,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>2016-17-206</t>
+          <t>2016-17-0206</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>2016-17-206</t>
+          <t>2016-17-0206</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -32796,7 +32796,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>2016-17-206</t>
+          <t>2016-17-0206</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -32838,7 +32838,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>2016-17-206</t>
+          <t>2016-17-0206</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -32880,7 +32880,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>2016-17-206</t>
+          <t>2016-17-0206</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -32922,7 +32922,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>2016-17-206</t>
+          <t>2016-17-0206</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -32964,7 +32964,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>2016-17-206</t>
+          <t>2016-17-0206</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -33006,7 +33006,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>2016-17-206</t>
+          <t>2016-17-0206</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -33048,7 +33048,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>2016-17-206</t>
+          <t>2016-17-0206</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -33090,7 +33090,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>2016-17-207</t>
+          <t>2016-17-0207</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -33132,7 +33132,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>2016-17-207</t>
+          <t>2016-17-0207</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -33174,7 +33174,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>2016-17-207</t>
+          <t>2016-17-0207</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -33216,7 +33216,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>2016-17-208</t>
+          <t>2016-17-0208</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>2016-17-208</t>
+          <t>2016-17-0208</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -33300,7 +33300,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>2016-17-208</t>
+          <t>2016-17-0208</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -33342,7 +33342,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>2016-17-208</t>
+          <t>2016-17-0208</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -33384,7 +33384,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>2016-17-208</t>
+          <t>2016-17-0208</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -33426,7 +33426,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>2016-17-208</t>
+          <t>2016-17-0208</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -33468,7 +33468,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>2016-17-208</t>
+          <t>2016-17-0208</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -33510,7 +33510,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>2016-17-208</t>
+          <t>2016-17-0208</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -33552,7 +33552,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>2016-17-208</t>
+          <t>2016-17-0208</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -33594,7 +33594,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>2016-17-208</t>
+          <t>2016-17-0208</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -33636,7 +33636,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>2016-17-208</t>
+          <t>2016-17-0208</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -33678,7 +33678,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>2016-17-208</t>
+          <t>2016-17-0208</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -33720,7 +33720,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>2016-17-209</t>
+          <t>2016-17-0209</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -33762,7 +33762,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>2016-17-209</t>
+          <t>2016-17-0209</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -33804,7 +33804,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>2016-17-209</t>
+          <t>2016-17-0209</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -33846,7 +33846,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>2016-17-209</t>
+          <t>2016-17-0209</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -33888,7 +33888,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>2016-17-209</t>
+          <t>2016-17-0209</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -33930,7 +33930,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>2016-17-210</t>
+          <t>2016-17-0210</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -33972,7 +33972,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>2016-17-210</t>
+          <t>2016-17-0210</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -34014,7 +34014,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>2016-17-210</t>
+          <t>2016-17-0210</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -34056,7 +34056,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>2016-17-210</t>
+          <t>2016-17-0210</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -34098,7 +34098,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>2016-17-210</t>
+          <t>2016-17-0210</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -34140,7 +34140,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>2016-17-210</t>
+          <t>2016-17-0210</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>2016-17-210</t>
+          <t>2016-17-0210</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -34224,7 +34224,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>2016-17-210</t>
+          <t>2016-17-0210</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -34266,7 +34266,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>2016-17-210</t>
+          <t>2016-17-0210</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -34308,7 +34308,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>2016-17-211</t>
+          <t>2016-17-0211</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -34350,7 +34350,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>2016-17-211</t>
+          <t>2016-17-0211</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -34392,7 +34392,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>2016-17-211</t>
+          <t>2016-17-0211</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -34434,7 +34434,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>2016-17-211</t>
+          <t>2016-17-0211</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -34476,7 +34476,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>2016-17-211</t>
+          <t>2016-17-0211</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -34518,7 +34518,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>2016-17-211</t>
+          <t>2016-17-0211</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>2016-17-211</t>
+          <t>2016-17-0211</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -34602,7 +34602,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>2016-17-211</t>
+          <t>2016-17-0211</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -34644,7 +34644,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>2016-17-212</t>
+          <t>2016-17-0212</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -34686,7 +34686,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>2016-17-212</t>
+          <t>2016-17-0212</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -34728,7 +34728,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>2016-17-212</t>
+          <t>2016-17-0212</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>2016-17-212</t>
+          <t>2016-17-0212</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -34812,7 +34812,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>2016-17-213</t>
+          <t>2016-17-0213</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -34854,7 +34854,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>2016-17-213</t>
+          <t>2016-17-0213</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -34896,7 +34896,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>2016-17-213</t>
+          <t>2016-17-0213</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -34938,7 +34938,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>2016-17-213</t>
+          <t>2016-17-0213</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -34980,7 +34980,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>2016-17-213</t>
+          <t>2016-17-0213</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -35022,7 +35022,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>2016-17-213</t>
+          <t>2016-17-0213</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -35064,7 +35064,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>2016-17-213</t>
+          <t>2016-17-0213</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -35106,7 +35106,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>2016-17-213</t>
+          <t>2016-17-0213</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -35148,7 +35148,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>2016-17-213</t>
+          <t>2016-17-0213</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -35190,7 +35190,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>2016-17-213</t>
+          <t>2016-17-0213</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -35232,7 +35232,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>2016-17-213</t>
+          <t>2016-17-0213</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -35274,7 +35274,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>2016-17-214</t>
+          <t>2016-17-0214</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
@@ -35316,7 +35316,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>2016-17-214</t>
+          <t>2016-17-0214</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -35358,7 +35358,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>2016-17-214</t>
+          <t>2016-17-0214</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
@@ -35400,7 +35400,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>2016-17-215</t>
+          <t>2016-17-0215</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -35442,7 +35442,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>2016-17-215</t>
+          <t>2016-17-0215</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -35484,7 +35484,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>2016-17-215</t>
+          <t>2016-17-0215</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -35526,7 +35526,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>2016-17-215</t>
+          <t>2016-17-0215</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -35568,7 +35568,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>2016-17-215</t>
+          <t>2016-17-0215</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -35610,7 +35610,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>2016-17-215</t>
+          <t>2016-17-0215</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -35652,7 +35652,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>2016-17-215</t>
+          <t>2016-17-0215</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -35694,7 +35694,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>2016-17-215</t>
+          <t>2016-17-0215</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -35736,7 +35736,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>2016-17-215</t>
+          <t>2016-17-0215</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -35778,7 +35778,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>2016-17-215</t>
+          <t>2016-17-0215</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -35820,7 +35820,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>2016-17-215</t>
+          <t>2016-17-0215</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -35862,7 +35862,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>2016-17-215</t>
+          <t>2016-17-0215</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -35904,7 +35904,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>2016-17-215</t>
+          <t>2016-17-0215</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -35946,7 +35946,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>2016-17-215</t>
+          <t>2016-17-0215</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -35988,7 +35988,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>2016-17-216</t>
+          <t>2016-17-0216</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -36030,7 +36030,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>2016-17-216</t>
+          <t>2016-17-0216</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -36072,7 +36072,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>2016-17-223</t>
+          <t>2016-17-0223</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>2016-17-223</t>
+          <t>2016-17-0223</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -36156,7 +36156,7 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>2016-17-223</t>
+          <t>2016-17-0223</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -36198,7 +36198,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>2016-17-223</t>
+          <t>2016-17-0223</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -36240,7 +36240,7 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>2016-17-223</t>
+          <t>2016-17-0223</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -36282,7 +36282,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>2016-17-223</t>
+          <t>2016-17-0223</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -36324,7 +36324,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>2016-17-224</t>
+          <t>2016-17-0224</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>2016-17-224</t>
+          <t>2016-17-0224</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -36408,7 +36408,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>2016-17-224</t>
+          <t>2016-17-0224</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -36450,7 +36450,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>2016-17-224</t>
+          <t>2016-17-0224</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -36492,7 +36492,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>2016-17-224</t>
+          <t>2016-17-0224</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -36534,7 +36534,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>2016-17-224</t>
+          <t>2016-17-0224</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -36576,7 +36576,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>2016-17-224</t>
+          <t>2016-17-0224</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -36618,7 +36618,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>2016-17-224</t>
+          <t>2016-17-0224</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -36660,7 +36660,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>2016-17-224</t>
+          <t>2016-17-0224</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
@@ -36702,7 +36702,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>2016-17-224</t>
+          <t>2016-17-0224</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -36744,7 +36744,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>2016-17-225</t>
+          <t>2016-17-0225</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -36786,7 +36786,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>2016-17-225</t>
+          <t>2016-17-0225</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -36828,7 +36828,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>2016-17-225</t>
+          <t>2016-17-0225</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -36870,7 +36870,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>2016-17-225</t>
+          <t>2016-17-0225</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>2016-17-225</t>
+          <t>2016-17-0225</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -36954,7 +36954,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>2016-17-225</t>
+          <t>2016-17-0225</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -36996,7 +36996,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>2016-17-225</t>
+          <t>2016-17-0225</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>2016-17-225</t>
+          <t>2016-17-0225</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -37080,7 +37080,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>2016-17-226</t>
+          <t>2016-17-0226</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -37122,7 +37122,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>2016-17-226</t>
+          <t>2016-17-0226</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>2016-17-226</t>
+          <t>2016-17-0226</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -37206,7 +37206,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>2016-17-226</t>
+          <t>2016-17-0226</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -37248,7 +37248,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>2016-17-226</t>
+          <t>2016-17-0226</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>2016-17-226</t>
+          <t>2016-17-0226</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
@@ -37332,7 +37332,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>2016-17-226</t>
+          <t>2016-17-0226</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -37374,7 +37374,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>2016-17-226</t>
+          <t>2016-17-0226</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>2016-17-227</t>
+          <t>2016-17-0227</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -37458,7 +37458,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>2016-17-227</t>
+          <t>2016-17-0227</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
@@ -37500,7 +37500,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>2016-17-227</t>
+          <t>2016-17-0227</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>2016-17-227</t>
+          <t>2016-17-0227</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
@@ -37584,7 +37584,7 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>2016-17-227</t>
+          <t>2016-17-0227</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -37626,7 +37626,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>2016-17-227</t>
+          <t>2016-17-0227</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>2016-17-227</t>
+          <t>2016-17-0227</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -37710,7 +37710,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>2016-17-228</t>
+          <t>2016-17-0228</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
@@ -37752,7 +37752,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>2016-17-228</t>
+          <t>2016-17-0228</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>2016-17-228</t>
+          <t>2016-17-0228</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
@@ -37836,7 +37836,7 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>2016-17-228</t>
+          <t>2016-17-0228</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -37878,7 +37878,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>2016-17-228</t>
+          <t>2016-17-0228</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>2016-17-228</t>
+          <t>2016-17-0228</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -37962,7 +37962,7 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>2016-17-301</t>
+          <t>2016-17-0301</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
@@ -38004,7 +38004,7 @@
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>2016-17-301</t>
+          <t>2016-17-0301</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>2016-17-301</t>
+          <t>2016-17-0301</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
@@ -38088,7 +38088,7 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>2016-17-301</t>
+          <t>2016-17-0301</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -38130,7 +38130,7 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>2016-17-301</t>
+          <t>2016-17-0301</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>2016-17-301</t>
+          <t>2016-17-0301</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -38214,7 +38214,7 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>2016-17-301</t>
+          <t>2016-17-0301</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -38256,7 +38256,7 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>2016-17-301</t>
+          <t>2016-17-0301</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>2016-17-301</t>
+          <t>2016-17-0301</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -38340,7 +38340,7 @@
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>2016-17-301</t>
+          <t>2016-17-0301</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
@@ -38382,7 +38382,7 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>2016-17-301</t>
+          <t>2016-17-0301</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>2016-17-302</t>
+          <t>2016-17-0302</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -38466,7 +38466,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>2016-17-302</t>
+          <t>2016-17-0302</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
@@ -38508,7 +38508,7 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>2016-17-302</t>
+          <t>2016-17-0302</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>2016-17-303</t>
+          <t>2016-17-0303</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
@@ -38592,7 +38592,7 @@
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>2016-17-303</t>
+          <t>2016-17-0303</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
@@ -38634,7 +38634,7 @@
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>2016-17-303</t>
+          <t>2016-17-0303</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>2016-17-303</t>
+          <t>2016-17-0303</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>2016-17-303</t>
+          <t>2016-17-0303</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
@@ -38760,7 +38760,7 @@
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>2016-17-303</t>
+          <t>2016-17-0303</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>2016-17-303</t>
+          <t>2016-17-0303</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
@@ -38844,7 +38844,7 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>2016-17-303</t>
+          <t>2016-17-0303</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -38886,7 +38886,7 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>2016-17-303</t>
+          <t>2016-17-0303</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>2016-17-303</t>
+          <t>2016-17-0303</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -38970,7 +38970,7 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>2016-17-304</t>
+          <t>2016-17-0304</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
@@ -39012,7 +39012,7 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>2016-17-304</t>
+          <t>2016-17-0304</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>2016-17-304</t>
+          <t>2016-17-0304</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
@@ -39096,7 +39096,7 @@
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>2016-17-304</t>
+          <t>2016-17-0304</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -39138,7 +39138,7 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>2016-17-304</t>
+          <t>2016-17-0304</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>2016-17-304</t>
+          <t>2016-17-0304</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -39222,7 +39222,7 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>2016-17-304</t>
+          <t>2016-17-0304</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
@@ -39264,7 +39264,7 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>2016-17-304</t>
+          <t>2016-17-0304</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>2016-17-305</t>
+          <t>2016-17-0305</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
@@ -39348,7 +39348,7 @@
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>2016-17-305</t>
+          <t>2016-17-0305</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
@@ -39390,7 +39390,7 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>2016-17-305</t>
+          <t>2016-17-0305</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>2016-17-305</t>
+          <t>2016-17-0305</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -39474,7 +39474,7 @@
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>2016-17-305</t>
+          <t>2016-17-0305</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
@@ -39516,7 +39516,7 @@
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>2016-17-305</t>
+          <t>2016-17-0305</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>2016-17-305</t>
+          <t>2016-17-0305</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
@@ -39600,7 +39600,7 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>2016-17-306</t>
+          <t>2016-17-0306</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -39642,7 +39642,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>2016-17-306</t>
+          <t>2016-17-0306</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>2016-17-306</t>
+          <t>2016-17-0306</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -39726,7 +39726,7 @@
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>2016-17-306</t>
+          <t>2016-17-0306</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
@@ -39768,7 +39768,7 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>2016-17-306</t>
+          <t>2016-17-0306</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>2016-17-306</t>
+          <t>2016-17-0306</t>
         </is>
       </c>
       <c r="C940" t="inlineStr">
@@ -39852,7 +39852,7 @@
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>2016-17-306</t>
+          <t>2016-17-0306</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
@@ -39894,7 +39894,7 @@
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>2016-17-306</t>
+          <t>2016-17-0306</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>2016-17-306</t>
+          <t>2016-17-0306</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
@@ -39978,7 +39978,7 @@
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>2016-17-306</t>
+          <t>2016-17-0306</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
@@ -40020,7 +40020,7 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>2016-17-306</t>
+          <t>2016-17-0306</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>2016-17-307</t>
+          <t>2016-17-0307</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
@@ -40104,7 +40104,7 @@
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>2016-17-307</t>
+          <t>2016-17-0307</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
@@ -40146,7 +40146,7 @@
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>2016-17-307</t>
+          <t>2016-17-0307</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>2016-17-308</t>
+          <t>2016-17-0308</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
@@ -40230,7 +40230,7 @@
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>2016-17-308</t>
+          <t>2016-17-0308</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
@@ -40272,7 +40272,7 @@
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>2016-17-308</t>
+          <t>2016-17-0308</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>2016-17-308</t>
+          <t>2016-17-0308</t>
         </is>
       </c>
       <c r="C952" t="inlineStr">
@@ -40356,7 +40356,7 @@
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>2016-17-308</t>
+          <t>2016-17-0308</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
@@ -40398,7 +40398,7 @@
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>2016-17-308</t>
+          <t>2016-17-0308</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>2016-17-308</t>
+          <t>2016-17-0308</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
@@ -40482,7 +40482,7 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>2016-17-308</t>
+          <t>2016-17-0308</t>
         </is>
       </c>
       <c r="C956" t="inlineStr">
@@ -40524,7 +40524,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>2016-17-308</t>
+          <t>2016-17-0308</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>2016-17-308</t>
+          <t>2016-17-0308</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
@@ -40608,7 +40608,7 @@
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>2016-17-308</t>
+          <t>2016-17-0308</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
@@ -40650,7 +40650,7 @@
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>2016-17-309</t>
+          <t>2016-17-0309</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>2016-17-309</t>
+          <t>2016-17-0309</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
@@ -40734,7 +40734,7 @@
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>2016-17-309</t>
+          <t>2016-17-0309</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
@@ -40776,7 +40776,7 @@
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>2016-17-309</t>
+          <t>2016-17-0309</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>2016-17-309</t>
+          <t>2016-17-0309</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
@@ -40860,7 +40860,7 @@
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>2016-17-310</t>
+          <t>2016-17-0310</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
@@ -40902,7 +40902,7 @@
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>2016-17-310</t>
+          <t>2016-17-0310</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>2016-17-310</t>
+          <t>2016-17-0310</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
@@ -40986,7 +40986,7 @@
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>2016-17-310</t>
+          <t>2016-17-0310</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
@@ -41028,7 +41028,7 @@
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>2016-17-310</t>
+          <t>2016-17-0310</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>2016-17-310</t>
+          <t>2016-17-0310</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
@@ -41112,7 +41112,7 @@
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>2016-17-310</t>
+          <t>2016-17-0310</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
@@ -41154,7 +41154,7 @@
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>2016-17-310</t>
+          <t>2016-17-0310</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>2016-17-311</t>
+          <t>2016-17-0311</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
@@ -41238,7 +41238,7 @@
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>2016-17-311</t>
+          <t>2016-17-0311</t>
         </is>
       </c>
       <c r="C974" t="inlineStr">
@@ -41280,7 +41280,7 @@
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>2016-17-311</t>
+          <t>2016-17-0311</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>2016-17-311</t>
+          <t>2016-17-0311</t>
         </is>
       </c>
       <c r="C976" t="inlineStr">
@@ -41364,7 +41364,7 @@
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>2016-17-311</t>
+          <t>2016-17-0311</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
@@ -41406,7 +41406,7 @@
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>2016-17-311</t>
+          <t>2016-17-0311</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>2016-17-311</t>
+          <t>2016-17-0311</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
@@ -41490,7 +41490,7 @@
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>2016-17-311</t>
+          <t>2016-17-0311</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>2016-17-311</t>
+          <t>2016-17-0311</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>2016-17-311</t>
+          <t>2016-17-0311</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
@@ -41616,7 +41616,7 @@
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>2016-17-311</t>
+          <t>2016-17-0311</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
@@ -41658,7 +41658,7 @@
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>2016-17-311</t>
+          <t>2016-17-0311</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>2016-17-312</t>
+          <t>2016-17-0312</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
@@ -41742,7 +41742,7 @@
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>2016-17-312</t>
+          <t>2016-17-0312</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
@@ -41784,7 +41784,7 @@
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>2016-17-312</t>
+          <t>2016-17-0312</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>2016-17-312</t>
+          <t>2016-17-0312</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
@@ -41868,7 +41868,7 @@
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>2016-17-312</t>
+          <t>2016-17-0312</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
@@ -41910,7 +41910,7 @@
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>2016-17-312</t>
+          <t>2016-17-0312</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>2016-17-313</t>
+          <t>2016-17-0313</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
@@ -41994,7 +41994,7 @@
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>2016-17-313</t>
+          <t>2016-17-0313</t>
         </is>
       </c>
       <c r="C992" t="inlineStr">
@@ -42036,7 +42036,7 @@
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>2016-17-313</t>
+          <t>2016-17-0313</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>2016-17-313</t>
+          <t>2016-17-0313</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
@@ -42120,7 +42120,7 @@
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>2016-17-313</t>
+          <t>2016-17-0313</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -42162,7 +42162,7 @@
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>2016-17-313</t>
+          <t>2016-17-0313</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>2016-17-313</t>
+          <t>2016-17-0313</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
@@ -42246,7 +42246,7 @@
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>2016-17-313</t>
+          <t>2016-17-0313</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
@@ -42288,7 +42288,7 @@
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>2016-17-314</t>
+          <t>2016-17-0314</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>2016-17-314</t>
+          <t>2016-17-0314</t>
         </is>
       </c>
       <c r="C1000" t="inlineStr">
@@ -42372,7 +42372,7 @@
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>2016-17-314</t>
+          <t>2016-17-0314</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
@@ -42414,7 +42414,7 @@
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>2016-17-314</t>
+          <t>2016-17-0314</t>
         </is>
       </c>
       <c r="C1002" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>2016-17-314</t>
+          <t>2016-17-0314</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
@@ -42498,7 +42498,7 @@
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>2016-17-315</t>
+          <t>2016-17-0315</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
@@ -42540,7 +42540,7 @@
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>2016-17-315</t>
+          <t>2016-17-0315</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>2016-17-315</t>
+          <t>2016-17-0315</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
@@ -42624,7 +42624,7 @@
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>2016-17-315</t>
+          <t>2016-17-0315</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -42666,7 +42666,7 @@
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>2016-17-315</t>
+          <t>2016-17-0315</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>2016-17-315</t>
+          <t>2016-17-0315</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
@@ -42750,7 +42750,7 @@
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>2016-17-315</t>
+          <t>2016-17-0315</t>
         </is>
       </c>
       <c r="C1010" t="inlineStr">
@@ -42792,7 +42792,7 @@
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>2016-17-315</t>
+          <t>2016-17-0315</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>2016-17-315</t>
+          <t>2016-17-0315</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
@@ -42876,7 +42876,7 @@
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>2016-17-315</t>
+          <t>2016-17-0315</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
@@ -42918,7 +42918,7 @@
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>2016-17-316</t>
+          <t>2016-17-0316</t>
         </is>
       </c>
       <c r="C1014" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>2016-17-316</t>
+          <t>2016-17-0316</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
@@ -43002,7 +43002,7 @@
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>2016-17-316</t>
+          <t>2016-17-0316</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
@@ -43044,7 +43044,7 @@
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>2016-17-316</t>
+          <t>2016-17-0316</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>2016-17-316</t>
+          <t>2016-17-0316</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
@@ -43128,7 +43128,7 @@
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>2016-17-316</t>
+          <t>2016-17-0316</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
@@ -43170,7 +43170,7 @@
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>2016-17-317</t>
+          <t>2016-17-0317</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>2016-17-317</t>
+          <t>2016-17-0317</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
@@ -43254,7 +43254,7 @@
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>2016-17-317</t>
+          <t>2016-17-0317</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
@@ -43296,7 +43296,7 @@
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>2016-17-317</t>
+          <t>2016-17-0317</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>2016-17-317</t>
+          <t>2016-17-0317</t>
         </is>
       </c>
       <c r="C1024" t="inlineStr">
@@ -43380,7 +43380,7 @@
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>2016-17-317</t>
+          <t>2016-17-0317</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
@@ -43422,7 +43422,7 @@
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>2016-17-317</t>
+          <t>2016-17-0317</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>2016-17-317</t>
+          <t>2016-17-0317</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
@@ -43506,7 +43506,7 @@
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>2016-17-318</t>
+          <t>2016-17-0318</t>
         </is>
       </c>
       <c r="C1028" t="inlineStr">
@@ -43548,7 +43548,7 @@
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>2016-17-318</t>
+          <t>2016-17-0318</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>2016-17-318</t>
+          <t>2016-17-0318</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
@@ -43632,7 +43632,7 @@
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>2016-17-318</t>
+          <t>2016-17-0318</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
@@ -43674,7 +43674,7 @@
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>2016-17-318</t>
+          <t>2016-17-0318</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>2016-17-318</t>
+          <t>2016-17-0318</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
@@ -43758,7 +43758,7 @@
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>2016-17-318</t>
+          <t>2016-17-0318</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
@@ -43800,7 +43800,7 @@
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>2016-17-318</t>
+          <t>2016-17-0318</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>2016-17-319</t>
+          <t>2016-17-0319</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
@@ -43884,7 +43884,7 @@
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>2016-17-319</t>
+          <t>2016-17-0319</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
@@ -43926,7 +43926,7 @@
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>2016-17-319</t>
+          <t>2016-17-0319</t>
         </is>
       </c>
       <c r="C1038" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>2016-17-319</t>
+          <t>2016-17-0319</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
@@ -44010,7 +44010,7 @@
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>2016-17-319</t>
+          <t>2016-17-0319</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
@@ -44052,7 +44052,7 @@
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>2016-17-319</t>
+          <t>2016-17-0319</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>2016-17-319</t>
+          <t>2016-17-0319</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
@@ -44136,7 +44136,7 @@
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>2016-17-319</t>
+          <t>2016-17-0319</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
@@ -44178,7 +44178,7 @@
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>2016-17-320</t>
+          <t>2016-17-0320</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>2016-17-320</t>
+          <t>2016-17-0320</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
@@ -44262,7 +44262,7 @@
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>2016-17-320</t>
+          <t>2016-17-0320</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
@@ -44304,7 +44304,7 @@
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>2016-17-320</t>
+          <t>2016-17-0320</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>2016-17-320</t>
+          <t>2016-17-0320</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
@@ -44388,7 +44388,7 @@
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>2016-17-320</t>
+          <t>2016-17-0320</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
@@ -44430,7 +44430,7 @@
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>2016-17-320</t>
+          <t>2016-17-0320</t>
         </is>
       </c>
       <c r="C1050" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>2016-17-321</t>
+          <t>2016-17-0321</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
@@ -44514,7 +44514,7 @@
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>2016-17-321</t>
+          <t>2016-17-0321</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
@@ -44556,7 +44556,7 @@
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>2016-17-321</t>
+          <t>2016-17-0321</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>2016-17-321</t>
+          <t>2016-17-0321</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
@@ -44640,7 +44640,7 @@
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>2016-17-321</t>
+          <t>2016-17-0321</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
@@ -44682,7 +44682,7 @@
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>2016-17-321</t>
+          <t>2016-17-0321</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>2016-17-321</t>
+          <t>2016-17-0321</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
@@ -44766,7 +44766,7 @@
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>2016-17-321</t>
+          <t>2016-17-0321</t>
         </is>
       </c>
       <c r="C1058" t="inlineStr">
@@ -44808,7 +44808,7 @@
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>2016-17-322</t>
+          <t>2016-17-0322</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>2016-17-322</t>
+          <t>2016-17-0322</t>
         </is>
       </c>
       <c r="C1060" t="inlineStr">
@@ -44892,7 +44892,7 @@
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>2016-17-322</t>
+          <t>2016-17-0322</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
@@ -44934,7 +44934,7 @@
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>2016-17-322</t>
+          <t>2016-17-0322</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>2016-17-322</t>
+          <t>2016-17-0322</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
@@ -45018,7 +45018,7 @@
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>2016-17-322</t>
+          <t>2016-17-0322</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
@@ -45060,7 +45060,7 @@
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>2016-17-322</t>
+          <t>2016-17-0322</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>2016-17-322</t>
+          <t>2016-17-0322</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
@@ -45144,7 +45144,7 @@
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>2016-17-323</t>
+          <t>2016-17-0323</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
@@ -45186,7 +45186,7 @@
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>2016-17-323</t>
+          <t>2016-17-0323</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>2016-17-323</t>
+          <t>2016-17-0323</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
@@ -45270,7 +45270,7 @@
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>2016-17-323</t>
+          <t>2016-17-0323</t>
         </is>
       </c>
       <c r="C1070" t="inlineStr">
@@ -45312,7 +45312,7 @@
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>2016-17-323</t>
+          <t>2016-17-0323</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>2016-17-324</t>
+          <t>2016-17-0324</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
@@ -45396,7 +45396,7 @@
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>2016-17-324</t>
+          <t>2016-17-0324</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
@@ -45438,7 +45438,7 @@
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>2016-17-324</t>
+          <t>2016-17-0324</t>
         </is>
       </c>
       <c r="C1074" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>2016-17-324</t>
+          <t>2016-17-0324</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
@@ -45522,7 +45522,7 @@
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>2016-17-324</t>
+          <t>2016-17-0324</t>
         </is>
       </c>
       <c r="C1076" t="inlineStr">
@@ -45564,7 +45564,7 @@
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>2016-17-324</t>
+          <t>2016-17-0324</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>2016-17-324</t>
+          <t>2016-17-0324</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
@@ -45648,7 +45648,7 @@
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>2016-17-324</t>
+          <t>2016-17-0324</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
@@ -45690,7 +45690,7 @@
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>2016-17-324</t>
+          <t>2016-17-0324</t>
         </is>
       </c>
       <c r="C1080" t="inlineStr">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>2016-17-324</t>
+          <t>2016-17-0324</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
@@ -45774,7 +45774,7 @@
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>2016-17-325</t>
+          <t>2016-17-0325</t>
         </is>
       </c>
       <c r="C1082" t="inlineStr">
@@ -45816,7 +45816,7 @@
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>2016-17-325</t>
+          <t>2016-17-0325</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>2016-17-325</t>
+          <t>2016-17-0325</t>
         </is>
       </c>
       <c r="C1084" t="inlineStr">
@@ -45900,7 +45900,7 @@
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>2016-17-325</t>
+          <t>2016-17-0325</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
@@ -45942,7 +45942,7 @@
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t>2016-17-325</t>
+          <t>2016-17-0325</t>
         </is>
       </c>
       <c r="C1086" t="inlineStr">
@@ -45984,7 +45984,7 @@
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>2016-17-326</t>
+          <t>2016-17-0326</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
@@ -46026,7 +46026,7 @@
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t>2016-17-326</t>
+          <t>2016-17-0326</t>
         </is>
       </c>
       <c r="C1088" t="inlineStr">
@@ -46068,7 +46068,7 @@
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>2016-17-326</t>
+          <t>2016-17-0326</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>2016-17-326</t>
+          <t>2016-17-0326</t>
         </is>
       </c>
       <c r="C1090" t="inlineStr">
@@ -46152,7 +46152,7 @@
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>2016-17-326</t>
+          <t>2016-17-0326</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
@@ -46194,7 +46194,7 @@
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>2016-17-326</t>
+          <t>2016-17-0326</t>
         </is>
       </c>
       <c r="C1092" t="inlineStr">
@@ -46236,7 +46236,7 @@
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>2016-17-326</t>
+          <t>2016-17-0326</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
@@ -46278,7 +46278,7 @@
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>2016-17-326</t>
+          <t>2016-17-0326</t>
         </is>
       </c>
       <c r="C1094" t="inlineStr">
@@ -46320,7 +46320,7 @@
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>2016-17-326</t>
+          <t>2016-17-0326</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
@@ -46362,7 +46362,7 @@
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>2016-17-326</t>
+          <t>2016-17-0326</t>
         </is>
       </c>
       <c r="C1096" t="inlineStr">
@@ -46404,7 +46404,7 @@
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>2016-17-327</t>
+          <t>2016-17-0327</t>
         </is>
       </c>
       <c r="C1097" t="inlineStr">
@@ -46446,7 +46446,7 @@
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>2016-17-327</t>
+          <t>2016-17-0327</t>
         </is>
       </c>
       <c r="C1098" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>2016-17-327</t>
+          <t>2016-17-0327</t>
         </is>
       </c>
       <c r="C1099" t="inlineStr">
@@ -46530,7 +46530,7 @@
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>2016-17-327</t>
+          <t>2016-17-0327</t>
         </is>
       </c>
       <c r="C1100" t="inlineStr">
@@ -46572,7 +46572,7 @@
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>2016-17-327</t>
+          <t>2016-17-0327</t>
         </is>
       </c>
       <c r="C1101" t="inlineStr">
@@ -46614,7 +46614,7 @@
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>2016-17-327</t>
+          <t>2016-17-0327</t>
         </is>
       </c>
       <c r="C1102" t="inlineStr">
@@ -46656,7 +46656,7 @@
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>2016-17-328</t>
+          <t>2016-17-0328</t>
         </is>
       </c>
       <c r="C1103" t="inlineStr">
@@ -46698,7 +46698,7 @@
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>2016-17-328</t>
+          <t>2016-17-0328</t>
         </is>
       </c>
       <c r="C1104" t="inlineStr">
@@ -46740,7 +46740,7 @@
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>2016-17-328</t>
+          <t>2016-17-0328</t>
         </is>
       </c>
       <c r="C1105" t="inlineStr">
@@ -46782,7 +46782,7 @@
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>2016-17-328</t>
+          <t>2016-17-0328</t>
         </is>
       </c>
       <c r="C1106" t="inlineStr">
@@ -46824,7 +46824,7 @@
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>2016-17-328</t>
+          <t>2016-17-0328</t>
         </is>
       </c>
       <c r="C1107" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>2016-17-328</t>
+          <t>2016-17-0328</t>
         </is>
       </c>
       <c r="C1108" t="inlineStr">
@@ -46908,7 +46908,7 @@
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>2016-17-328</t>
+          <t>2016-17-0328</t>
         </is>
       </c>
       <c r="C1109" t="inlineStr">
@@ -46950,7 +46950,7 @@
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>2016-17-328</t>
+          <t>2016-17-0328</t>
         </is>
       </c>
       <c r="C1110" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>2016-17-329</t>
+          <t>2016-17-0329</t>
         </is>
       </c>
       <c r="C1111" t="inlineStr">
@@ -47034,7 +47034,7 @@
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>2016-17-329</t>
+          <t>2016-17-0329</t>
         </is>
       </c>
       <c r="C1112" t="inlineStr">
@@ -47076,7 +47076,7 @@
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>2016-17-329</t>
+          <t>2016-17-0329</t>
         </is>
       </c>
       <c r="C1113" t="inlineStr">
@@ -47118,7 +47118,7 @@
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>2016-17-329</t>
+          <t>2016-17-0329</t>
         </is>
       </c>
       <c r="C1114" t="inlineStr">
@@ -47160,7 +47160,7 @@
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>2016-17-329</t>
+          <t>2016-17-0329</t>
         </is>
       </c>
       <c r="C1115" t="inlineStr">
@@ -47202,7 +47202,7 @@
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>2016-17-329</t>
+          <t>2016-17-0329</t>
         </is>
       </c>
       <c r="C1116" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>2016-17-329</t>
+          <t>2016-17-0329</t>
         </is>
       </c>
       <c r="C1117" t="inlineStr">
@@ -47286,7 +47286,7 @@
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>2016-17-329</t>
+          <t>2016-17-0329</t>
         </is>
       </c>
       <c r="C1118" t="inlineStr">
@@ -47328,7 +47328,7 @@
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>2016-17-329</t>
+          <t>2016-17-0329</t>
         </is>
       </c>
       <c r="C1119" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>2016-17-329</t>
+          <t>2016-17-0329</t>
         </is>
       </c>
       <c r="C1120" t="inlineStr">
@@ -47412,7 +47412,7 @@
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>2016-17-330</t>
+          <t>2016-17-0330</t>
         </is>
       </c>
       <c r="C1121" t="inlineStr">
@@ -47454,7 +47454,7 @@
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>2016-17-330</t>
+          <t>2016-17-0330</t>
         </is>
       </c>
       <c r="C1122" t="inlineStr">
@@ -47496,7 +47496,7 @@
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>2016-17-330</t>
+          <t>2016-17-0330</t>
         </is>
       </c>
       <c r="C1123" t="inlineStr">
@@ -47538,7 +47538,7 @@
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>2016-17-330</t>
+          <t>2016-17-0330</t>
         </is>
       </c>
       <c r="C1124" t="inlineStr">
@@ -47580,7 +47580,7 @@
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>2016-17-330</t>
+          <t>2016-17-0330</t>
         </is>
       </c>
       <c r="C1125" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>2016-17-331</t>
+          <t>2016-17-0331</t>
         </is>
       </c>
       <c r="C1126" t="inlineStr">
@@ -47664,7 +47664,7 @@
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>2016-17-331</t>
+          <t>2016-17-0331</t>
         </is>
       </c>
       <c r="C1127" t="inlineStr">
@@ -47706,7 +47706,7 @@
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>2016-17-331</t>
+          <t>2016-17-0331</t>
         </is>
       </c>
       <c r="C1128" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>2016-17-331</t>
+          <t>2016-17-0331</t>
         </is>
       </c>
       <c r="C1129" t="inlineStr">
@@ -47790,7 +47790,7 @@
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>2016-17-331</t>
+          <t>2016-17-0331</t>
         </is>
       </c>
       <c r="C1130" t="inlineStr">
@@ -47832,7 +47832,7 @@
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>2016-17-331</t>
+          <t>2016-17-0331</t>
         </is>
       </c>
       <c r="C1131" t="inlineStr">
@@ -47874,7 +47874,7 @@
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>2016-17-331</t>
+          <t>2016-17-0331</t>
         </is>
       </c>
       <c r="C1132" t="inlineStr">
@@ -47916,7 +47916,7 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>2016-17-331</t>
+          <t>2016-17-0331</t>
         </is>
       </c>
       <c r="C1133" t="inlineStr">
@@ -47958,7 +47958,7 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>2016-17-331</t>
+          <t>2016-17-0331</t>
         </is>
       </c>
       <c r="C1134" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>2016-17-331</t>
+          <t>2016-17-0331</t>
         </is>
       </c>
       <c r="C1135" t="inlineStr">
@@ -48042,7 +48042,7 @@
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>2016-17-331</t>
+          <t>2016-17-0331</t>
         </is>
       </c>
       <c r="C1136" t="inlineStr">
@@ -48084,7 +48084,7 @@
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>2016-17-401</t>
+          <t>2016-17-0401</t>
         </is>
       </c>
       <c r="C1137" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>2016-17-401</t>
+          <t>2016-17-0401</t>
         </is>
       </c>
       <c r="C1138" t="inlineStr">
@@ -48168,7 +48168,7 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>2016-17-401</t>
+          <t>2016-17-0401</t>
         </is>
       </c>
       <c r="C1139" t="inlineStr">
@@ -48210,7 +48210,7 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>2016-17-401</t>
+          <t>2016-17-0401</t>
         </is>
       </c>
       <c r="C1140" t="inlineStr">
@@ -48252,7 +48252,7 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>2016-17-401</t>
+          <t>2016-17-0401</t>
         </is>
       </c>
       <c r="C1141" t="inlineStr">
@@ -48294,7 +48294,7 @@
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>2016-17-402</t>
+          <t>2016-17-0402</t>
         </is>
       </c>
       <c r="C1142" t="inlineStr">
@@ -48336,7 +48336,7 @@
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>2016-17-402</t>
+          <t>2016-17-0402</t>
         </is>
       </c>
       <c r="C1143" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>2016-17-402</t>
+          <t>2016-17-0402</t>
         </is>
       </c>
       <c r="C1144" t="inlineStr">
@@ -48420,7 +48420,7 @@
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>2016-17-402</t>
+          <t>2016-17-0402</t>
         </is>
       </c>
       <c r="C1145" t="inlineStr">
@@ -48462,7 +48462,7 @@
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>2016-17-402</t>
+          <t>2016-17-0402</t>
         </is>
       </c>
       <c r="C1146" t="inlineStr">
@@ -48504,7 +48504,7 @@
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>2016-17-402</t>
+          <t>2016-17-0402</t>
         </is>
       </c>
       <c r="C1147" t="inlineStr">
@@ -48546,7 +48546,7 @@
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>2016-17-402</t>
+          <t>2016-17-0402</t>
         </is>
       </c>
       <c r="C1148" t="inlineStr">
@@ -48588,7 +48588,7 @@
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>2016-17-402</t>
+          <t>2016-17-0402</t>
         </is>
       </c>
       <c r="C1149" t="inlineStr">
@@ -48630,7 +48630,7 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>2016-17-402</t>
+          <t>2016-17-0402</t>
         </is>
       </c>
       <c r="C1150" t="inlineStr">
@@ -48672,7 +48672,7 @@
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>2016-17-402</t>
+          <t>2016-17-0402</t>
         </is>
       </c>
       <c r="C1151" t="inlineStr">
@@ -48714,7 +48714,7 @@
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>2016-17-402</t>
+          <t>2016-17-0402</t>
         </is>
       </c>
       <c r="C1152" t="inlineStr">
@@ -48756,7 +48756,7 @@
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>2016-17-402</t>
+          <t>2016-17-0402</t>
         </is>
       </c>
       <c r="C1153" t="inlineStr">
@@ -48798,7 +48798,7 @@
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>2016-17-403</t>
+          <t>2016-17-0403</t>
         </is>
       </c>
       <c r="C1154" t="inlineStr">
@@ -48840,7 +48840,7 @@
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>2016-17-404</t>
+          <t>2016-17-0404</t>
         </is>
       </c>
       <c r="C1155" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>2016-17-404</t>
+          <t>2016-17-0404</t>
         </is>
       </c>
       <c r="C1156" t="inlineStr">
@@ -48924,7 +48924,7 @@
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>2016-17-404</t>
+          <t>2016-17-0404</t>
         </is>
       </c>
       <c r="C1157" t="inlineStr">
@@ -48966,7 +48966,7 @@
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>2016-17-404</t>
+          <t>2016-17-0404</t>
         </is>
       </c>
       <c r="C1158" t="inlineStr">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>2016-17-404</t>
+          <t>2016-17-0404</t>
         </is>
       </c>
       <c r="C1159" t="inlineStr">
@@ -49050,7 +49050,7 @@
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>2016-17-404</t>
+          <t>2016-17-0404</t>
         </is>
       </c>
       <c r="C1160" t="inlineStr">
@@ -49092,7 +49092,7 @@
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>2016-17-404</t>
+          <t>2016-17-0404</t>
         </is>
       </c>
       <c r="C1161" t="inlineStr">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>2016-17-404</t>
+          <t>2016-17-0404</t>
         </is>
       </c>
       <c r="C1162" t="inlineStr">
@@ -49176,7 +49176,7 @@
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t>2016-17-404</t>
+          <t>2016-17-0404</t>
         </is>
       </c>
       <c r="C1163" t="inlineStr">
@@ -49218,7 +49218,7 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>2016-17-404</t>
+          <t>2016-17-0404</t>
         </is>
       </c>
       <c r="C1164" t="inlineStr">
@@ -49260,7 +49260,7 @@
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>2016-17-404</t>
+          <t>2016-17-0404</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
@@ -49302,7 +49302,7 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>2016-17-405</t>
+          <t>2016-17-0405</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
@@ -49344,7 +49344,7 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>2016-17-405</t>
+          <t>2016-17-0405</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
@@ -49386,7 +49386,7 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>2016-17-405</t>
+          <t>2016-17-0405</t>
         </is>
       </c>
       <c r="C1168" t="inlineStr">
@@ -49428,7 +49428,7 @@
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>2016-17-405</t>
+          <t>2016-17-0405</t>
         </is>
       </c>
       <c r="C1169" t="inlineStr">
@@ -49470,7 +49470,7 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>2016-17-405</t>
+          <t>2016-17-0405</t>
         </is>
       </c>
       <c r="C1170" t="inlineStr">
@@ -49512,7 +49512,7 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>2016-17-405</t>
+          <t>2016-17-0405</t>
         </is>
       </c>
       <c r="C1171" t="inlineStr">
@@ -49554,7 +49554,7 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>2016-17-405</t>
+          <t>2016-17-0405</t>
         </is>
       </c>
       <c r="C1172" t="inlineStr">
@@ -49596,7 +49596,7 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>2016-17-405</t>
+          <t>2016-17-0405</t>
         </is>
       </c>
       <c r="C1173" t="inlineStr">
@@ -49638,7 +49638,7 @@
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>2016-17-406</t>
+          <t>2016-17-0406</t>
         </is>
       </c>
       <c r="C1174" t="inlineStr">
@@ -49680,7 +49680,7 @@
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>2016-17-406</t>
+          <t>2016-17-0406</t>
         </is>
       </c>
       <c r="C1175" t="inlineStr">
@@ -49722,7 +49722,7 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>2016-17-406</t>
+          <t>2016-17-0406</t>
         </is>
       </c>
       <c r="C1176" t="inlineStr">
@@ -49764,7 +49764,7 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>2016-17-406</t>
+          <t>2016-17-0406</t>
         </is>
       </c>
       <c r="C1177" t="inlineStr">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>2016-17-406</t>
+          <t>2016-17-0406</t>
         </is>
       </c>
       <c r="C1178" t="inlineStr">
@@ -49848,7 +49848,7 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>2016-17-406</t>
+          <t>2016-17-0406</t>
         </is>
       </c>
       <c r="C1179" t="inlineStr">
@@ -49890,7 +49890,7 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>2016-17-407</t>
+          <t>2016-17-0407</t>
         </is>
       </c>
       <c r="C1180" t="inlineStr">
@@ -49932,7 +49932,7 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>2016-17-407</t>
+          <t>2016-17-0407</t>
         </is>
       </c>
       <c r="C1181" t="inlineStr">
@@ -49974,7 +49974,7 @@
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>2016-17-407</t>
+          <t>2016-17-0407</t>
         </is>
       </c>
       <c r="C1182" t="inlineStr">
@@ -50016,7 +50016,7 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>2016-17-407</t>
+          <t>2016-17-0407</t>
         </is>
       </c>
       <c r="C1183" t="inlineStr">
@@ -50058,7 +50058,7 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>2016-17-407</t>
+          <t>2016-17-0407</t>
         </is>
       </c>
       <c r="C1184" t="inlineStr">
@@ -50100,7 +50100,7 @@
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>2016-17-407</t>
+          <t>2016-17-0407</t>
         </is>
       </c>
       <c r="C1185" t="inlineStr">
@@ -50142,7 +50142,7 @@
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>2016-17-407</t>
+          <t>2016-17-0407</t>
         </is>
       </c>
       <c r="C1186" t="inlineStr">
@@ -50184,7 +50184,7 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>2016-17-407</t>
+          <t>2016-17-0407</t>
         </is>
       </c>
       <c r="C1187" t="inlineStr">
@@ -50226,7 +50226,7 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>2016-17-407</t>
+          <t>2016-17-0407</t>
         </is>
       </c>
       <c r="C1188" t="inlineStr">
@@ -50268,7 +50268,7 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>2016-17-408</t>
+          <t>2016-17-0408</t>
         </is>
       </c>
       <c r="C1189" t="inlineStr">
@@ -50310,7 +50310,7 @@
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>2016-17-408</t>
+          <t>2016-17-0408</t>
         </is>
       </c>
       <c r="C1190" t="inlineStr">
@@ -50352,7 +50352,7 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>2016-17-408</t>
+          <t>2016-17-0408</t>
         </is>
       </c>
       <c r="C1191" t="inlineStr">
@@ -50394,7 +50394,7 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>2016-17-408</t>
+          <t>2016-17-0408</t>
         </is>
       </c>
       <c r="C1192" t="inlineStr">
@@ -50436,7 +50436,7 @@
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>2016-17-408</t>
+          <t>2016-17-0408</t>
         </is>
       </c>
       <c r="C1193" t="inlineStr">
@@ -50478,7 +50478,7 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>2016-17-408</t>
+          <t>2016-17-0408</t>
         </is>
       </c>
       <c r="C1194" t="inlineStr">
@@ -50520,7 +50520,7 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>2016-17-408</t>
+          <t>2016-17-0408</t>
         </is>
       </c>
       <c r="C1195" t="inlineStr">
@@ -50562,7 +50562,7 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>2016-17-408</t>
+          <t>2016-17-0408</t>
         </is>
       </c>
       <c r="C1196" t="inlineStr">
@@ -50604,7 +50604,7 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>2016-17-409</t>
+          <t>2016-17-0409</t>
         </is>
       </c>
       <c r="C1197" t="inlineStr">
@@ -50646,7 +50646,7 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>2016-17-409</t>
+          <t>2016-17-0409</t>
         </is>
       </c>
       <c r="C1198" t="inlineStr">
@@ -50688,7 +50688,7 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>2016-17-409</t>
+          <t>2016-17-0409</t>
         </is>
       </c>
       <c r="C1199" t="inlineStr">
@@ -50730,7 +50730,7 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>2016-17-409</t>
+          <t>2016-17-0409</t>
         </is>
       </c>
       <c r="C1200" t="inlineStr">
@@ -50772,7 +50772,7 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>2016-17-409</t>
+          <t>2016-17-0409</t>
         </is>
       </c>
       <c r="C1201" t="inlineStr">
@@ -50814,7 +50814,7 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>2016-17-409</t>
+          <t>2016-17-0409</t>
         </is>
       </c>
       <c r="C1202" t="inlineStr">
@@ -50856,7 +50856,7 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>2016-17-409</t>
+          <t>2016-17-0409</t>
         </is>
       </c>
       <c r="C1203" t="inlineStr">
@@ -50898,7 +50898,7 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>2016-17-410</t>
+          <t>2016-17-0410</t>
         </is>
       </c>
       <c r="C1204" t="inlineStr">
@@ -50940,7 +50940,7 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>2016-17-410</t>
+          <t>2016-17-0410</t>
         </is>
       </c>
       <c r="C1205" t="inlineStr">
@@ -50982,7 +50982,7 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>2016-17-410</t>
+          <t>2016-17-0410</t>
         </is>
       </c>
       <c r="C1206" t="inlineStr">
@@ -51024,7 +51024,7 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>2016-17-410</t>
+          <t>2016-17-0410</t>
         </is>
       </c>
       <c r="C1207" t="inlineStr">
@@ -51066,7 +51066,7 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>2016-17-410</t>
+          <t>2016-17-0410</t>
         </is>
       </c>
       <c r="C1208" t="inlineStr">
@@ -51108,7 +51108,7 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>2016-17-410</t>
+          <t>2016-17-0410</t>
         </is>
       </c>
       <c r="C1209" t="inlineStr">
@@ -51150,7 +51150,7 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>2016-17-410</t>
+          <t>2016-17-0410</t>
         </is>
       </c>
       <c r="C1210" t="inlineStr">
@@ -51192,7 +51192,7 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>2016-17-410</t>
+          <t>2016-17-0410</t>
         </is>
       </c>
       <c r="C1211" t="inlineStr">
@@ -51234,7 +51234,7 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>2016-17-410</t>
+          <t>2016-17-0410</t>
         </is>
       </c>
       <c r="C1212" t="inlineStr">
@@ -51276,7 +51276,7 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>2016-17-411</t>
+          <t>2016-17-0411</t>
         </is>
       </c>
       <c r="C1213" t="inlineStr">
@@ -51318,7 +51318,7 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>2016-17-411</t>
+          <t>2016-17-0411</t>
         </is>
       </c>
       <c r="C1214" t="inlineStr">
@@ -51360,7 +51360,7 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>2016-17-411</t>
+          <t>2016-17-0411</t>
         </is>
       </c>
       <c r="C1215" t="inlineStr">
@@ -51402,7 +51402,7 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>2016-17-411</t>
+          <t>2016-17-0411</t>
         </is>
       </c>
       <c r="C1216" t="inlineStr">
@@ -51444,7 +51444,7 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>2016-17-411</t>
+          <t>2016-17-0411</t>
         </is>
       </c>
       <c r="C1217" t="inlineStr">
@@ -51486,7 +51486,7 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>2016-17-412</t>
+          <t>2016-17-0412</t>
         </is>
       </c>
       <c r="C1218" t="inlineStr">
@@ -51528,7 +51528,7 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>2016-17-412</t>
+          <t>2016-17-0412</t>
         </is>
       </c>
       <c r="C1219" t="inlineStr">
@@ -51570,7 +51570,7 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>2016-17-412</t>
+          <t>2016-17-0412</t>
         </is>
       </c>
       <c r="C1220" t="inlineStr">
@@ -51612,7 +51612,7 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>2016-17-412</t>
+          <t>2016-17-0412</t>
         </is>
       </c>
       <c r="C1221" t="inlineStr">
@@ -51654,7 +51654,7 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>2016-17-412</t>
+          <t>2016-17-0412</t>
         </is>
       </c>
       <c r="C1222" t="inlineStr">
@@ -51696,7 +51696,7 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>2016-17-412</t>
+          <t>2016-17-0412</t>
         </is>
       </c>
       <c r="C1223" t="inlineStr">
@@ -51738,7 +51738,7 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>2016-17-412</t>
+          <t>2016-17-0412</t>
         </is>
       </c>
       <c r="C1224" t="inlineStr">
@@ -51780,7 +51780,7 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>2016-17-412</t>
+          <t>2016-17-0412</t>
         </is>
       </c>
       <c r="C1225" t="inlineStr">
@@ -51822,7 +51822,7 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>2016-17-412</t>
+          <t>2016-17-0412</t>
         </is>
       </c>
       <c r="C1226" t="inlineStr">
@@ -51864,7 +51864,7 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>2016-17-412</t>
+          <t>2016-17-0412</t>
         </is>
       </c>
       <c r="C1227" t="inlineStr">
@@ -51906,7 +51906,7 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>2016-17-412</t>
+          <t>2016-17-0412</t>
         </is>
       </c>
       <c r="C1228" t="inlineStr">
@@ -51948,7 +51948,7 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>2016-17-412</t>
+          <t>2016-17-0412</t>
         </is>
       </c>
       <c r="C1229" t="inlineStr">
@@ -51990,7 +51990,7 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>2016-17-412</t>
+          <t>2016-17-0412</t>
         </is>
       </c>
       <c r="C1230" t="inlineStr">
@@ -52032,7 +52032,7 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>2016-17-412</t>
+          <t>2016-17-0412</t>
         </is>
       </c>
       <c r="C1231" t="inlineStr">
@@ -52074,7 +52074,7 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>2016-17-415</t>
+          <t>2016-17-0415</t>
         </is>
       </c>
       <c r="C1232" t="inlineStr">
@@ -52116,7 +52116,7 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>2016-17-415</t>
+          <t>2016-17-0415</t>
         </is>
       </c>
       <c r="C1233" t="inlineStr">
@@ -52158,7 +52158,7 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>2016-17-415</t>
+          <t>2016-17-0415</t>
         </is>
       </c>
       <c r="C1234" t="inlineStr">
@@ -52200,7 +52200,7 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>2016-17-415</t>
+          <t>2016-17-0415</t>
         </is>
       </c>
       <c r="C1235" t="inlineStr">
@@ -52242,7 +52242,7 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>2016-17-416</t>
+          <t>2016-17-0416</t>
         </is>
       </c>
       <c r="C1236" t="inlineStr">
@@ -52284,7 +52284,7 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>2016-17-416</t>
+          <t>2016-17-0416</t>
         </is>
       </c>
       <c r="C1237" t="inlineStr">
@@ -52326,7 +52326,7 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>2016-17-416</t>
+          <t>2016-17-0416</t>
         </is>
       </c>
       <c r="C1238" t="inlineStr">
@@ -52368,7 +52368,7 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>2016-17-416</t>
+          <t>2016-17-0416</t>
         </is>
       </c>
       <c r="C1239" t="inlineStr">
@@ -52410,7 +52410,7 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>2016-17-417</t>
+          <t>2016-17-0417</t>
         </is>
       </c>
       <c r="C1240" t="inlineStr">
@@ -52452,7 +52452,7 @@
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>2016-17-417</t>
+          <t>2016-17-0417</t>
         </is>
       </c>
       <c r="C1241" t="inlineStr">
@@ -52494,7 +52494,7 @@
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>2016-17-418</t>
+          <t>2016-17-0418</t>
         </is>
       </c>
       <c r="C1242" t="inlineStr">
@@ -52536,7 +52536,7 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>2016-17-418</t>
+          <t>2016-17-0418</t>
         </is>
       </c>
       <c r="C1243" t="inlineStr">
@@ -52578,7 +52578,7 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>2016-17-418</t>
+          <t>2016-17-0418</t>
         </is>
       </c>
       <c r="C1244" t="inlineStr">
@@ -52620,7 +52620,7 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>2016-17-419</t>
+          <t>2016-17-0419</t>
         </is>
       </c>
       <c r="C1245" t="inlineStr">
@@ -52662,7 +52662,7 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>2016-17-419</t>
+          <t>2016-17-0419</t>
         </is>
       </c>
       <c r="C1246" t="inlineStr">
@@ -52704,7 +52704,7 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>2016-17-419</t>
+          <t>2016-17-0419</t>
         </is>
       </c>
       <c r="C1247" t="inlineStr">
@@ -52746,7 +52746,7 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>2016-17-420</t>
+          <t>2016-17-0420</t>
         </is>
       </c>
       <c r="C1248" t="inlineStr">
@@ -52788,7 +52788,7 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>2016-17-420</t>
+          <t>2016-17-0420</t>
         </is>
       </c>
       <c r="C1249" t="inlineStr">
@@ -52830,7 +52830,7 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>2016-17-420</t>
+          <t>2016-17-0420</t>
         </is>
       </c>
       <c r="C1250" t="inlineStr">
@@ -52872,7 +52872,7 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>2016-17-421</t>
+          <t>2016-17-0421</t>
         </is>
       </c>
       <c r="C1251" t="inlineStr">
@@ -52914,7 +52914,7 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>2016-17-421</t>
+          <t>2016-17-0421</t>
         </is>
       </c>
       <c r="C1252" t="inlineStr">
@@ -52956,7 +52956,7 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>2016-17-421</t>
+          <t>2016-17-0421</t>
         </is>
       </c>
       <c r="C1253" t="inlineStr">
@@ -52998,7 +52998,7 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>2016-17-422</t>
+          <t>2016-17-0422</t>
         </is>
       </c>
       <c r="C1254" t="inlineStr">
@@ -53040,7 +53040,7 @@
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>2016-17-422</t>
+          <t>2016-17-0422</t>
         </is>
       </c>
       <c r="C1255" t="inlineStr">
@@ -53082,7 +53082,7 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>2016-17-422</t>
+          <t>2016-17-0422</t>
         </is>
       </c>
       <c r="C1256" t="inlineStr">
@@ -53124,7 +53124,7 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>2016-17-422</t>
+          <t>2016-17-0422</t>
         </is>
       </c>
       <c r="C1257" t="inlineStr">
@@ -53166,7 +53166,7 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>2016-17-423</t>
+          <t>2016-17-0423</t>
         </is>
       </c>
       <c r="C1258" t="inlineStr">
@@ -53208,7 +53208,7 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>2016-17-423</t>
+          <t>2016-17-0423</t>
         </is>
       </c>
       <c r="C1259" t="inlineStr">
@@ -53250,7 +53250,7 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>2016-17-423</t>
+          <t>2016-17-0423</t>
         </is>
       </c>
       <c r="C1260" t="inlineStr">
@@ -53292,7 +53292,7 @@
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>2016-17-423</t>
+          <t>2016-17-0423</t>
         </is>
       </c>
       <c r="C1261" t="inlineStr">
@@ -53334,7 +53334,7 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>2016-17-424</t>
+          <t>2016-17-0424</t>
         </is>
       </c>
       <c r="C1262" t="inlineStr">
@@ -53376,7 +53376,7 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>2016-17-424</t>
+          <t>2016-17-0424</t>
         </is>
       </c>
       <c r="C1263" t="inlineStr">
@@ -53418,7 +53418,7 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>2016-17-424</t>
+          <t>2016-17-0424</t>
         </is>
       </c>
       <c r="C1264" t="inlineStr">
@@ -53460,7 +53460,7 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>2016-17-425</t>
+          <t>2016-17-0425</t>
         </is>
       </c>
       <c r="C1265" t="inlineStr">
@@ -53502,7 +53502,7 @@
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>2016-17-425</t>
+          <t>2016-17-0425</t>
         </is>
       </c>
       <c r="C1266" t="inlineStr">
@@ -53544,7 +53544,7 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>2016-17-425</t>
+          <t>2016-17-0425</t>
         </is>
       </c>
       <c r="C1267" t="inlineStr">
@@ -53586,7 +53586,7 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>2016-17-426</t>
+          <t>2016-17-0426</t>
         </is>
       </c>
       <c r="C1268" t="inlineStr">
@@ -53628,7 +53628,7 @@
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>2016-17-426</t>
+          <t>2016-17-0426</t>
         </is>
       </c>
       <c r="C1269" t="inlineStr">
@@ -53670,7 +53670,7 @@
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>2016-17-427</t>
+          <t>2016-17-0427</t>
         </is>
       </c>
       <c r="C1270" t="inlineStr">
@@ -53712,7 +53712,7 @@
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>2016-17-427</t>
+          <t>2016-17-0427</t>
         </is>
       </c>
       <c r="C1271" t="inlineStr">
@@ -53754,7 +53754,7 @@
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>2016-17-428</t>
+          <t>2016-17-0428</t>
         </is>
       </c>
       <c r="C1272" t="inlineStr">
@@ -53796,7 +53796,7 @@
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>2016-17-428</t>
+          <t>2016-17-0428</t>
         </is>
       </c>
       <c r="C1273" t="inlineStr">
@@ -53838,7 +53838,7 @@
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>2016-17-428</t>
+          <t>2016-17-0428</t>
         </is>
       </c>
       <c r="C1274" t="inlineStr">
@@ -53880,7 +53880,7 @@
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>2016-17-430</t>
+          <t>2016-17-0430</t>
         </is>
       </c>
       <c r="C1275" t="inlineStr">
@@ -53922,7 +53922,7 @@
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>2016-17-430</t>
+          <t>2016-17-0430</t>
         </is>
       </c>
       <c r="C1276" t="inlineStr">
@@ -53964,7 +53964,7 @@
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>2016-17-501</t>
+          <t>2016-17-0501</t>
         </is>
       </c>
       <c r="C1277" t="inlineStr">
@@ -54006,7 +54006,7 @@
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>2016-17-501</t>
+          <t>2016-17-0501</t>
         </is>
       </c>
       <c r="C1278" t="inlineStr">
@@ -54048,7 +54048,7 @@
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>2016-17-502</t>
+          <t>2016-17-0502</t>
         </is>
       </c>
       <c r="C1279" t="inlineStr">
@@ -54090,7 +54090,7 @@
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>2016-17-502</t>
+          <t>2016-17-0502</t>
         </is>
       </c>
       <c r="C1280" t="inlineStr">
@@ -54132,7 +54132,7 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>2016-17-503</t>
+          <t>2016-17-0503</t>
         </is>
       </c>
       <c r="C1281" t="inlineStr">
@@ -54174,7 +54174,7 @@
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>2016-17-503</t>
+          <t>2016-17-0503</t>
         </is>
       </c>
       <c r="C1282" t="inlineStr">
@@ -54216,7 +54216,7 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>2016-17-504</t>
+          <t>2016-17-0504</t>
         </is>
       </c>
       <c r="C1283" t="inlineStr">
@@ -54258,7 +54258,7 @@
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>2016-17-504</t>
+          <t>2016-17-0504</t>
         </is>
       </c>
       <c r="C1284" t="inlineStr">
@@ -54300,7 +54300,7 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>2016-17-505</t>
+          <t>2016-17-0505</t>
         </is>
       </c>
       <c r="C1285" t="inlineStr">
@@ -54342,7 +54342,7 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>2016-17-505</t>
+          <t>2016-17-0505</t>
         </is>
       </c>
       <c r="C1286" t="inlineStr">
@@ -54384,7 +54384,7 @@
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>2016-17-506</t>
+          <t>2016-17-0506</t>
         </is>
       </c>
       <c r="C1287" t="inlineStr">
@@ -54426,7 +54426,7 @@
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>2016-17-506</t>
+          <t>2016-17-0506</t>
         </is>
       </c>
       <c r="C1288" t="inlineStr">
@@ -54468,7 +54468,7 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>2016-17-506</t>
+          <t>2016-17-0506</t>
         </is>
       </c>
       <c r="C1289" t="inlineStr">
@@ -54510,7 +54510,7 @@
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>2016-17-507</t>
+          <t>2016-17-0507</t>
         </is>
       </c>
       <c r="C1290" t="inlineStr">
@@ -54552,7 +54552,7 @@
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>2016-17-508</t>
+          <t>2016-17-0508</t>
         </is>
       </c>
       <c r="C1291" t="inlineStr">
@@ -54594,7 +54594,7 @@
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>2016-17-509</t>
+          <t>2016-17-0509</t>
         </is>
       </c>
       <c r="C1292" t="inlineStr">
@@ -54636,7 +54636,7 @@
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>2016-17-510</t>
+          <t>2016-17-0510</t>
         </is>
       </c>
       <c r="C1293" t="inlineStr">
@@ -54678,7 +54678,7 @@
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>2016-17-511</t>
+          <t>2016-17-0511</t>
         </is>
       </c>
       <c r="C1294" t="inlineStr">
@@ -54720,7 +54720,7 @@
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>2016-17-512</t>
+          <t>2016-17-0512</t>
         </is>
       </c>
       <c r="C1295" t="inlineStr">
@@ -54762,7 +54762,7 @@
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>2016-17-514</t>
+          <t>2016-17-0514</t>
         </is>
       </c>
       <c r="C1296" t="inlineStr">
@@ -54804,7 +54804,7 @@
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>2016-17-515</t>
+          <t>2016-17-0515</t>
         </is>
       </c>
       <c r="C1297" t="inlineStr">
@@ -54846,7 +54846,7 @@
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>2016-17-516</t>
+          <t>2016-17-0516</t>
         </is>
       </c>
       <c r="C1298" t="inlineStr">
@@ -54888,7 +54888,7 @@
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>2016-17-517</t>
+          <t>2016-17-0517</t>
         </is>
       </c>
       <c r="C1299" t="inlineStr">
@@ -54930,7 +54930,7 @@
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>2016-17-519</t>
+          <t>2016-17-0519</t>
         </is>
       </c>
       <c r="C1300" t="inlineStr">
@@ -54972,7 +54972,7 @@
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>2016-17-520</t>
+          <t>2016-17-0520</t>
         </is>
       </c>
       <c r="C1301" t="inlineStr">
@@ -55014,7 +55014,7 @@
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>2016-17-521</t>
+          <t>2016-17-0521</t>
         </is>
       </c>
       <c r="C1302" t="inlineStr">
@@ -55056,7 +55056,7 @@
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>2016-17-522</t>
+          <t>2016-17-0522</t>
         </is>
       </c>
       <c r="C1303" t="inlineStr">
@@ -55098,7 +55098,7 @@
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>2016-17-523</t>
+          <t>2016-17-0523</t>
         </is>
       </c>
       <c r="C1304" t="inlineStr">
@@ -55140,7 +55140,7 @@
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>2016-17-525</t>
+          <t>2016-17-0525</t>
         </is>
       </c>
       <c r="C1305" t="inlineStr">
@@ -55182,7 +55182,7 @@
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>2016-17-601</t>
+          <t>2016-17-0601</t>
         </is>
       </c>
       <c r="C1306" t="inlineStr">
@@ -55224,7 +55224,7 @@
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>2016-17-604</t>
+          <t>2016-17-0604</t>
         </is>
       </c>
       <c r="C1307" t="inlineStr">
@@ -55266,7 +55266,7 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>2016-17-607</t>
+          <t>2016-17-0607</t>
         </is>
       </c>
       <c r="C1308" t="inlineStr">
@@ -55308,7 +55308,7 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>2016-17-609</t>
+          <t>2016-17-0609</t>
         </is>
       </c>
       <c r="C1309" t="inlineStr">
@@ -55350,7 +55350,7 @@
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>2016-17-612</t>
+          <t>2016-17-0612</t>
         </is>
       </c>
       <c r="C1310" t="inlineStr">

--- a/Odds-Data-Clean/2016-17.xlsx
+++ b/Odds-Data-Clean/2016-17.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -54,18 +54,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -674,7 +674,11 @@
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E8" t="n">
         <v>209</v>
       </c>
@@ -796,7 +800,11 @@
           <t>Philadelphia 76ers</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E11" t="n">
         <v>208</v>
       </c>
@@ -1207,7 +1215,11 @@
           <t>2016-17-1028</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>Indiana Pacers</t>
@@ -1245,7 +1257,11 @@
           <t>2016-17-1028</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
@@ -1624,7 +1640,11 @@
           <t>Milwaukee Bucks</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E31" t="n">
         <v>206</v>
       </c>
@@ -1993,7 +2013,11 @@
           <t>2016-17-1030</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
@@ -2157,7 +2181,11 @@
           <t>2016-17-1031</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>Chicago Bulls</t>
@@ -2825,7 +2853,11 @@
           <t>2016-17-1102</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>Detroit Pistons</t>
@@ -3036,7 +3068,11 @@
           <t>Los Angeles Clippers</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E65" t="n">
         <v>205</v>
       </c>
@@ -3242,7 +3278,11 @@
           <t>Golden State Warriors</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E70" t="n">
         <v>226.5</v>
       </c>
@@ -3317,7 +3357,11 @@
           <t>2016-17-1104</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>Charlotte Bobcats</t>
@@ -3649,7 +3693,11 @@
           <t>2016-17-1105</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>Minnesota Timberwolves</t>
@@ -4359,7 +4407,11 @@
           <t>2016-17-1107</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>Miami Heat</t>
@@ -4565,7 +4617,11 @@
           <t>2016-17-1108</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
           <t>Minnesota Timberwolves</t>
@@ -4818,7 +4874,11 @@
           <t>New York Knicks</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E108" t="n">
         <v>211</v>
       </c>
@@ -5019,7 +5079,11 @@
           <t>2016-17-1109</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
@@ -5603,7 +5667,11 @@
           <t>2016-17-1111</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
           <t>Los Angeles Clippers</t>
@@ -6108,7 +6176,11 @@
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E139" t="n">
         <v>217.5</v>
       </c>
@@ -6267,7 +6339,11 @@
           <t>2016-17-1113</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D143" t="inlineStr">
         <is>
           <t>Orlando Magic</t>
@@ -6436,7 +6512,11 @@
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E147" t="n">
         <v>200</v>
       </c>
@@ -6684,7 +6764,11 @@
           <t>Los Angeles Clippers</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E153" t="n">
         <v>211</v>
       </c>
@@ -6890,7 +6974,11 @@
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E158" t="n">
         <v>219</v>
       </c>
@@ -7217,7 +7305,11 @@
           <t>2016-17-1116</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr"/>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D166" t="inlineStr">
         <is>
           <t>Houston Rockets</t>
@@ -7717,8 +7809,16 @@
           <t>2016-17-1118</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr"/>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E178" t="n">
         <v>218</v>
       </c>
@@ -8423,7 +8523,11 @@
           <t>2016-17-1120</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr"/>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D195" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
@@ -8461,7 +8565,11 @@
           <t>2016-17-1120</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr"/>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D196" t="inlineStr">
         <is>
           <t>Indiana Pacers</t>
@@ -9134,7 +9242,11 @@
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E212" t="n">
         <v>220</v>
       </c>
@@ -9419,7 +9531,11 @@
           <t>2016-17-1123</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr"/>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D219" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
@@ -9630,7 +9746,11 @@
           <t>Sacramento Kings</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E224" t="n">
         <v>208</v>
       </c>
@@ -10088,7 +10208,11 @@
           <t>Indiana Pacers</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E235" t="n">
         <v>214</v>
       </c>
@@ -10168,7 +10292,11 @@
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E237" t="n">
         <v>213.5</v>
       </c>
@@ -10411,7 +10539,11 @@
           <t>2016-17-1126</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr"/>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D243" t="inlineStr">
         <is>
           <t>Detroit Pistons</t>
@@ -10617,7 +10749,11 @@
           <t>2016-17-1127</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr"/>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D248" t="inlineStr">
         <is>
           <t>Sacramento Kings</t>
@@ -10954,7 +11090,11 @@
           <t>New York Knicks</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E256" t="n">
         <v>214.5</v>
       </c>
@@ -11197,7 +11337,11 @@
           <t>2016-17-1129</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr"/>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D262" t="inlineStr">
         <is>
           <t>Los Angeles Clippers</t>
@@ -11487,7 +11631,11 @@
           <t>2016-17-1130</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr"/>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D269" t="inlineStr">
         <is>
           <t>Washington Wizards</t>
@@ -11819,7 +11967,11 @@
           <t>2016-17-1201</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr"/>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D277" t="inlineStr">
         <is>
           <t>Milwaukee Bucks</t>
@@ -12408,7 +12560,11 @@
           <t>Milwaukee Bucks</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E291" t="n">
         <v>217</v>
       </c>
@@ -12819,7 +12975,11 @@
           <t>2016-17-1204</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr"/>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D301" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
@@ -12988,7 +13148,11 @@
           <t>Atlanta Hawks</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E305" t="n">
         <v>209.5</v>
       </c>
@@ -13063,7 +13227,11 @@
           <t>2016-17-1205</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr"/>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D307" t="inlineStr">
         <is>
           <t>Washington Wizards</t>
@@ -13731,7 +13899,11 @@
           <t>2016-17-1207</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr"/>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D323" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
@@ -14525,7 +14697,11 @@
           <t>2016-17-1209</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr"/>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D342" t="inlineStr">
         <is>
           <t>Houston Rockets</t>
@@ -14988,7 +15164,11 @@
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E353" t="n">
         <v>212</v>
       </c>
@@ -15147,7 +15327,11 @@
           <t>2016-17-1211</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr"/>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D357" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
@@ -15442,7 +15626,11 @@
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E364" t="n">
         <v>227.5</v>
       </c>
@@ -15816,7 +16004,11 @@
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E373" t="n">
         <v>219.5</v>
       </c>
@@ -16017,7 +16209,11 @@
           <t>2016-17-1214</t>
         </is>
       </c>
-      <c r="C378" t="inlineStr"/>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D378" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
@@ -16186,7 +16382,11 @@
           <t>Utah Jazz</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E382" t="n">
         <v>199</v>
       </c>
@@ -16476,7 +16676,11 @@
           <t>Orlando Magic</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E389" t="n">
         <v>219.5</v>
       </c>
@@ -16887,7 +17091,11 @@
           <t>2016-17-1217</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr"/>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D399" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
@@ -17224,7 +17432,11 @@
           <t>Philadelphia 76ers</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E407" t="n">
         <v>217.5</v>
       </c>
@@ -17509,7 +17721,11 @@
           <t>2016-17-1219</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D414" t="inlineStr">
         <is>
           <t>Atlanta Hawks</t>
@@ -17762,7 +17978,11 @@
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E420" t="n">
         <v>225</v>
       </c>
@@ -18304,7 +18524,11 @@
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E433" t="n">
         <v>210</v>
       </c>
@@ -18547,7 +18771,11 @@
           <t>2016-17-1222</t>
         </is>
       </c>
-      <c r="C439" t="inlineStr"/>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D439" t="inlineStr">
         <is>
           <t>Golden State Warriors</t>
@@ -18800,7 +19028,11 @@
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E445" t="n">
         <v>221</v>
       </c>
@@ -18838,7 +19070,11 @@
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E446" t="n">
         <v>209</v>
       </c>
@@ -19375,7 +19611,11 @@
           <t>2016-17-1225</t>
         </is>
       </c>
-      <c r="C459" t="inlineStr"/>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D459" t="inlineStr">
         <is>
           <t>Minnesota Timberwolves</t>
@@ -19581,7 +19821,11 @@
           <t>2016-17-1226</t>
         </is>
       </c>
-      <c r="C464" t="inlineStr"/>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D464" t="inlineStr">
         <is>
           <t>Charlotte Bobcats</t>
@@ -19960,7 +20204,11 @@
           <t>Miami Heat</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E473" t="n">
         <v>206</v>
       </c>
@@ -20250,7 +20498,11 @@
           <t>Chicago Bulls</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E480" t="n">
         <v>213.5</v>
       </c>
@@ -20582,7 +20834,11 @@
           <t>Memphis Grizzlies</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E488" t="n">
         <v>199.5</v>
       </c>
@@ -20788,7 +21044,11 @@
           <t>Washington Wizards</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E493" t="n">
         <v>220.5</v>
       </c>
@@ -21367,7 +21627,11 @@
           <t>2016-17-1231</t>
         </is>
       </c>
-      <c r="C507" t="inlineStr"/>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D507" t="inlineStr">
         <is>
           <t>Los Angeles Clippers</t>
@@ -21662,7 +21926,11 @@
           <t>Milwaukee Bucks</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E514" t="n">
         <v>212</v>
       </c>
@@ -21695,7 +21963,11 @@
           <t>2016-17-0102</t>
         </is>
       </c>
-      <c r="C515" t="inlineStr"/>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D515" t="inlineStr">
         <is>
           <t>Utah Jazz</t>
@@ -22326,7 +22598,11 @@
           <t>Charlotte Bobcats</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr"/>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E530" t="n">
         <v>210</v>
       </c>
@@ -22574,7 +22850,11 @@
           <t>Indiana Pacers</t>
         </is>
       </c>
-      <c r="D536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E536" t="n">
         <v>219</v>
       </c>
@@ -22696,7 +22976,11 @@
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E539" t="n">
         <v>224</v>
       </c>
@@ -22981,7 +23265,11 @@
           <t>2016-17-0106</t>
         </is>
       </c>
-      <c r="C546" t="inlineStr"/>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D546" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
@@ -23355,7 +23643,11 @@
           <t>2016-17-0107</t>
         </is>
       </c>
-      <c r="C555" t="inlineStr"/>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D555" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
@@ -23519,7 +23811,11 @@
           <t>2016-17-0108</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr"/>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D559" t="inlineStr">
         <is>
           <t>Philadelphia 76ers</t>
@@ -23982,7 +24278,11 @@
           <t>Chicago Bulls</t>
         </is>
       </c>
-      <c r="D570" t="inlineStr"/>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E570" t="n">
         <v>207</v>
       </c>
@@ -24099,7 +24399,11 @@
           <t>2016-17-0110</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr"/>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D573" t="inlineStr">
         <is>
           <t>Atlanta Hawks</t>
@@ -24473,7 +24777,11 @@
           <t>2016-17-0111</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr"/>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D582" t="inlineStr">
         <is>
           <t>Memphis Grizzlies</t>
@@ -24679,7 +24987,11 @@
           <t>2016-17-0112</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr"/>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D587" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
@@ -24932,7 +25244,11 @@
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="D593" t="inlineStr"/>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E593" t="n">
         <v>221.5</v>
       </c>
@@ -25096,7 +25412,11 @@
           <t>Minnesota Timberwolves</t>
         </is>
       </c>
-      <c r="D597" t="inlineStr"/>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E597" t="n">
         <v>209</v>
       </c>
@@ -25591,7 +25911,11 @@
           <t>2016-17-0115</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr"/>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D609" t="inlineStr">
         <is>
           <t>Houston Rockets</t>
@@ -25676,7 +26000,11 @@
           <t>Sacramento Kings</t>
         </is>
       </c>
-      <c r="D611" t="inlineStr"/>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E611" t="n">
         <v>212</v>
       </c>
@@ -26092,7 +26420,11 @@
           <t>Los Angeles Clippers</t>
         </is>
       </c>
-      <c r="D621" t="inlineStr"/>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E621" t="n">
         <v>210.5</v>
       </c>
@@ -26125,7 +26457,11 @@
           <t>2016-17-0117</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr"/>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D622" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
@@ -26672,7 +27008,11 @@
           <t>Golden State Warriors</t>
         </is>
       </c>
-      <c r="D635" t="inlineStr"/>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E635" t="n">
         <v>227</v>
       </c>
@@ -27046,7 +27386,11 @@
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="D644" t="inlineStr"/>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E644" t="n">
         <v>218.5</v>
       </c>
@@ -27378,7 +27722,11 @@
           <t>Charlotte Bobcats</t>
         </is>
       </c>
-      <c r="D652" t="inlineStr"/>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E652" t="n">
         <v>220</v>
       </c>
@@ -27999,7 +28347,11 @@
           <t>2016-17-0123</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr"/>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D667" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
@@ -28252,7 +28604,11 @@
           <t>Utah Jazz</t>
         </is>
       </c>
-      <c r="D673" t="inlineStr"/>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E673" t="n">
         <v>203</v>
       </c>
@@ -28621,7 +28977,11 @@
           <t>2016-17-0125</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr"/>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D682" t="inlineStr">
         <is>
           <t>Miami Heat</t>
@@ -28832,7 +29192,11 @@
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="D687" t="inlineStr"/>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E687" t="n">
         <v>215.5</v>
       </c>
@@ -28991,7 +29355,11 @@
           <t>2016-17-0126</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr"/>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D691" t="inlineStr">
         <is>
           <t>Dallas Mavericks</t>
@@ -29244,7 +29612,11 @@
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="D697" t="inlineStr"/>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E697" t="n">
         <v>226</v>
       </c>
@@ -29702,7 +30074,11 @@
           <t>Minnesota Timberwolves</t>
         </is>
       </c>
-      <c r="D708" t="inlineStr"/>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E708" t="n">
         <v>217.5</v>
       </c>
@@ -29866,7 +30242,11 @@
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="D712" t="inlineStr"/>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E712" t="n">
         <v>220.5</v>
       </c>
@@ -30156,7 +30536,11 @@
           <t>Miami Heat</t>
         </is>
       </c>
-      <c r="D719" t="inlineStr"/>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E719" t="n">
         <v>218.5</v>
       </c>
@@ -30530,7 +30914,11 @@
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="D728" t="inlineStr"/>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E728" t="n">
         <v>210</v>
       </c>
@@ -30773,7 +31161,11 @@
           <t>2016-17-0201</t>
         </is>
       </c>
-      <c r="C734" t="inlineStr"/>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D734" t="inlineStr">
         <is>
           <t>New York Knicks</t>
@@ -31063,7 +31455,11 @@
           <t>2016-17-0201</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr"/>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D741" t="inlineStr">
         <is>
           <t>Chicago Bulls</t>
@@ -31395,7 +31791,11 @@
           <t>2016-17-0203</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr"/>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D749" t="inlineStr">
         <is>
           <t>Indiana Pacers</t>
@@ -31433,7 +31833,11 @@
           <t>2016-17-0203</t>
         </is>
       </c>
-      <c r="C750" t="inlineStr"/>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D750" t="inlineStr">
         <is>
           <t>Memphis Grizzlies</t>
@@ -32101,7 +32505,11 @@
           <t>2016-17-0205</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr"/>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D766" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
@@ -32181,7 +32589,11 @@
           <t>2016-17-0205</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr"/>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D768" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
@@ -32308,7 +32720,11 @@
           <t>Indiana Pacers</t>
         </is>
       </c>
-      <c r="D771" t="inlineStr"/>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E771" t="n">
         <v>210.5</v>
       </c>
@@ -32682,7 +33098,11 @@
           <t>Charlotte Bobcats</t>
         </is>
       </c>
-      <c r="D780" t="inlineStr"/>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E780" t="n">
         <v>217</v>
       </c>
@@ -32967,7 +33387,11 @@
           <t>2016-17-0208</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr"/>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D787" t="inlineStr">
         <is>
           <t>Washington Wizards</t>
@@ -33383,7 +33807,11 @@
           <t>2016-17-0209</t>
         </is>
       </c>
-      <c r="C797" t="inlineStr"/>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D797" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
@@ -33505,7 +33933,11 @@
           <t>2016-17-0210</t>
         </is>
       </c>
-      <c r="C800" t="inlineStr"/>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D800" t="inlineStr">
         <is>
           <t>Miami Heat</t>
@@ -34047,7 +34479,11 @@
           <t>2016-17-0211</t>
         </is>
       </c>
-      <c r="C813" t="inlineStr"/>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D813" t="inlineStr">
         <is>
           <t>Golden State Warriors</t>
@@ -34426,7 +34862,11 @@
           <t>Washington Wizards</t>
         </is>
       </c>
-      <c r="D822" t="inlineStr"/>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E822" t="n">
         <v>218.5</v>
       </c>
@@ -34501,7 +34941,11 @@
           <t>2016-17-0213</t>
         </is>
       </c>
-      <c r="C824" t="inlineStr"/>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D824" t="inlineStr">
         <is>
           <t>Memphis Grizzlies</t>
@@ -35085,7 +35529,11 @@
           <t>2016-17-0215</t>
         </is>
       </c>
-      <c r="C838" t="inlineStr"/>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D838" t="inlineStr">
         <is>
           <t>Milwaukee Bucks</t>
@@ -35417,7 +35865,11 @@
           <t>2016-17-0215</t>
         </is>
       </c>
-      <c r="C846" t="inlineStr"/>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D846" t="inlineStr">
         <is>
           <t>New York Knicks</t>
@@ -36085,7 +36537,11 @@
           <t>2016-17-0224</t>
         </is>
       </c>
-      <c r="C862" t="inlineStr"/>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D862" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
@@ -36212,7 +36668,11 @@
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="D865" t="inlineStr"/>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E865" t="n">
         <v>231</v>
       </c>
@@ -36586,7 +37046,11 @@
           <t>Golden State Warriors</t>
         </is>
       </c>
-      <c r="D874" t="inlineStr"/>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E874" t="n">
         <v>233</v>
       </c>
@@ -36871,7 +37335,11 @@
           <t>2016-17-0226</t>
         </is>
       </c>
-      <c r="C881" t="inlineStr"/>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D881" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
@@ -37413,7 +37881,11 @@
           <t>2016-17-0228</t>
         </is>
       </c>
-      <c r="C894" t="inlineStr"/>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D894" t="inlineStr">
         <is>
           <t>Utah Jazz</t>
@@ -37918,7 +38390,11 @@
           <t>Sacramento Kings</t>
         </is>
       </c>
-      <c r="D906" t="inlineStr"/>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E906" t="n">
         <v>213.5</v>
       </c>
@@ -38040,7 +38516,11 @@
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="D909" t="inlineStr"/>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E909" t="n">
         <v>220</v>
       </c>
@@ -38330,7 +38810,11 @@
           <t>Utah Jazz</t>
         </is>
       </c>
-      <c r="D916" t="inlineStr"/>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E916" t="n">
         <v>206.5</v>
       </c>
@@ -38368,7 +38852,11 @@
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="D917" t="inlineStr"/>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E917" t="n">
         <v>225</v>
       </c>
@@ -38784,7 +39272,11 @@
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="D927" t="inlineStr"/>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E927" t="n">
         <v>227</v>
       </c>
@@ -39032,7 +39524,11 @@
           <t>Dallas Mavericks</t>
         </is>
       </c>
-      <c r="D933" t="inlineStr"/>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E933" t="n">
         <v>204</v>
       </c>
@@ -39364,7 +39860,11 @@
           <t>Memphis Grizzlies</t>
         </is>
       </c>
-      <c r="D941" t="inlineStr"/>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E941" t="n">
         <v>214</v>
       </c>
@@ -39565,7 +40065,11 @@
           <t>2016-17-0307</t>
         </is>
       </c>
-      <c r="C946" t="inlineStr"/>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D946" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
@@ -39776,7 +40280,11 @@
           <t>Atlanta Hawks</t>
         </is>
       </c>
-      <c r="D951" t="inlineStr"/>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E951" t="n">
         <v>219</v>
       </c>
@@ -40187,7 +40695,11 @@
           <t>2016-17-0309</t>
         </is>
       </c>
-      <c r="C961" t="inlineStr"/>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D961" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
@@ -40608,7 +41120,11 @@
           <t>Dallas Mavericks</t>
         </is>
       </c>
-      <c r="D971" t="inlineStr"/>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E971" t="n">
         <v>214</v>
       </c>
@@ -40683,7 +41199,11 @@
           <t>2016-17-0311</t>
         </is>
       </c>
-      <c r="C973" t="inlineStr"/>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D973" t="inlineStr">
         <is>
           <t>Utah Jazz</t>
@@ -41267,7 +41787,11 @@
           <t>2016-17-0312</t>
         </is>
       </c>
-      <c r="C987" t="inlineStr"/>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D987" t="inlineStr">
         <is>
           <t>New York Knicks</t>
@@ -41851,8 +42375,16 @@
           <t>2016-17-0314</t>
         </is>
       </c>
-      <c r="C1001" t="inlineStr"/>
-      <c r="D1001" t="inlineStr"/>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1001" t="n">
         <v>225</v>
       </c>
@@ -42436,7 +42968,11 @@
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="D1015" t="inlineStr"/>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1015" t="n">
         <v>208.5</v>
       </c>
@@ -42516,7 +43052,11 @@
           <t>New York Knicks</t>
         </is>
       </c>
-      <c r="D1017" t="inlineStr"/>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E1017" t="n">
         <v>219.5</v>
       </c>
@@ -42759,7 +43299,11 @@
           <t>2016-17-0317</t>
         </is>
       </c>
-      <c r="C1023" t="inlineStr"/>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D1023" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
@@ -42965,7 +43509,11 @@
           <t>2016-17-0318</t>
         </is>
       </c>
-      <c r="C1028" t="inlineStr"/>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1028" t="inlineStr">
         <is>
           <t>Sacramento Kings</t>
@@ -43297,7 +43845,11 @@
           <t>2016-17-0319</t>
         </is>
       </c>
-      <c r="C1036" t="inlineStr"/>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D1036" t="inlineStr">
         <is>
           <t>Dallas Mavericks</t>
@@ -43839,7 +44391,11 @@
           <t>2016-17-0320</t>
         </is>
       </c>
-      <c r="C1049" t="inlineStr"/>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1049" t="inlineStr">
         <is>
           <t>Golden State Warriors</t>
@@ -43961,7 +44517,11 @@
           <t>2016-17-0321</t>
         </is>
       </c>
-      <c r="C1052" t="inlineStr"/>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D1052" t="inlineStr">
         <is>
           <t>Detroit Pistons</t>
@@ -44419,7 +44979,11 @@
           <t>2016-17-0322</t>
         </is>
       </c>
-      <c r="C1063" t="inlineStr"/>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1063" t="inlineStr">
         <is>
           <t>Philadelphia 76ers</t>
@@ -44625,7 +45189,11 @@
           <t>2016-17-0323</t>
         </is>
       </c>
-      <c r="C1068" t="inlineStr"/>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D1068" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
@@ -44794,7 +45362,11 @@
           <t>Washington Wizards</t>
         </is>
       </c>
-      <c r="D1072" t="inlineStr"/>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E1072" t="n">
         <v>224</v>
       </c>
@@ -45420,7 +45992,11 @@
           <t>Atlanta Hawks</t>
         </is>
       </c>
-      <c r="D1087" t="inlineStr"/>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E1087" t="n">
         <v>214</v>
       </c>
@@ -45542,7 +46118,11 @@
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="D1090" t="inlineStr"/>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1090" t="n">
         <v>233</v>
       </c>
@@ -45958,7 +46538,11 @@
           <t>Dallas Mavericks</t>
         </is>
       </c>
-      <c r="D1100" t="inlineStr"/>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1100" t="n">
         <v>207</v>
       </c>
@@ -46243,7 +46827,11 @@
           <t>2016-17-0328</t>
         </is>
       </c>
-      <c r="C1107" t="inlineStr"/>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D1107" t="inlineStr">
         <is>
           <t>Philadelphia 76ers</t>
@@ -46454,7 +47042,11 @@
           <t>Orlando Magic</t>
         </is>
       </c>
-      <c r="D1112" t="inlineStr"/>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1112" t="n">
         <v>218</v>
       </c>
@@ -46828,7 +47420,11 @@
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="D1121" t="inlineStr"/>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E1121" t="n">
         <v>213</v>
       </c>
@@ -47407,7 +48003,11 @@
           <t>2016-17-0331</t>
         </is>
       </c>
-      <c r="C1135" t="inlineStr"/>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1135" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
@@ -47571,7 +48171,11 @@
           <t>2016-17-0401</t>
         </is>
       </c>
-      <c r="C1139" t="inlineStr"/>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D1139" t="inlineStr">
         <is>
           <t>Orlando Magic</t>
@@ -47735,7 +48339,11 @@
           <t>2016-17-0402</t>
         </is>
       </c>
-      <c r="C1143" t="inlineStr"/>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1143" t="inlineStr">
         <is>
           <t>Charlotte Bobcats</t>
@@ -47983,7 +48591,11 @@
           <t>2016-17-0402</t>
         </is>
       </c>
-      <c r="C1149" t="inlineStr"/>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D1149" t="inlineStr">
         <is>
           <t>Atlanta Hawks</t>
@@ -48236,7 +48848,11 @@
           <t>Philadelphia 76ers</t>
         </is>
       </c>
-      <c r="D1155" t="inlineStr"/>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E1155" t="n">
         <v>219</v>
       </c>
@@ -48437,7 +49053,11 @@
           <t>2016-17-0404</t>
         </is>
       </c>
-      <c r="C1160" t="inlineStr"/>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1160" t="inlineStr">
         <is>
           <t>Milwaukee Bucks</t>
@@ -48858,7 +49478,11 @@
           <t>Memphis Grizzlies</t>
         </is>
       </c>
-      <c r="D1170" t="inlineStr"/>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1170" t="n">
         <v>203</v>
       </c>
@@ -49022,7 +49646,11 @@
           <t>Orlando Magic</t>
         </is>
       </c>
-      <c r="D1174" t="inlineStr"/>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E1174" t="n">
         <v>227.5</v>
       </c>
@@ -49564,7 +50192,11 @@
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="D1187" t="inlineStr"/>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1187" t="n">
         <v>226</v>
       </c>
@@ -49639,7 +50271,11 @@
           <t>2016-17-0408</t>
         </is>
       </c>
-      <c r="C1189" t="inlineStr"/>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="D1189" t="inlineStr">
         <is>
           <t>Chicago Bulls</t>
@@ -50060,7 +50696,11 @@
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="D1199" t="inlineStr"/>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1199" t="n">
         <v>229</v>
       </c>
@@ -50350,7 +50990,11 @@
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="D1206" t="inlineStr"/>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E1206" t="n">
         <v>223</v>
       </c>
@@ -50682,7 +51326,11 @@
           <t>Minnesota Timberwolves</t>
         </is>
       </c>
-      <c r="D1214" t="inlineStr"/>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1214" t="n">
         <v>217</v>
       </c>
@@ -50925,7 +51573,11 @@
           <t>2016-17-0412</t>
         </is>
       </c>
-      <c r="C1220" t="inlineStr"/>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1220" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
@@ -51220,7 +51872,11 @@
           <t>Chicago Bulls</t>
         </is>
       </c>
-      <c r="D1227" t="inlineStr"/>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
       <c r="E1227" t="n">
         <v>214</v>
       </c>
@@ -51720,7 +52376,11 @@
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="D1239" t="inlineStr"/>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1239" t="n">
         <v>228</v>
       </c>
@@ -52010,7 +52670,11 @@
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="D1246" t="inlineStr"/>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1246" t="n">
         <v>224</v>
       </c>
@@ -52253,7 +52917,11 @@
           <t>2016-17-0421</t>
         </is>
       </c>
-      <c r="C1252" t="inlineStr"/>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1252" t="inlineStr">
         <is>
           <t>Houston Rockets</t>
@@ -52543,7 +53211,11 @@
           <t>2016-17-0423</t>
         </is>
       </c>
-      <c r="C1259" t="inlineStr"/>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1259" t="inlineStr">
         <is>
           <t>Houston Rockets</t>
@@ -52838,7 +53510,11 @@
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="D1266" t="inlineStr"/>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1266" t="n">
         <v>223.5</v>
       </c>
@@ -54711,6 +55387,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>